--- a/30_output_share/06_BRONZE노출감사.xlsx
+++ b/30_output_share/06_BRONZE노출감사.xlsx
@@ -5075,7 +5075,7 @@
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>동명 GOLD 컬럼 존재</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>동명 GOLD 컬럼 존재</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>동명 GOLD 컬럼 존재</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>동명 GOLD 컬럼 존재</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="F433" s="11" t="inlineStr">
         <is>
-          <t>동명 GOLD 컬럼 존재</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>

--- a/30_output_share/06_BRONZE노출감사.xlsx
+++ b/30_output_share/06_BRONZE노출감사.xlsx
@@ -16,10 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GA4" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_AGENCY'!$A$3:$F$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_AGENCY'!$A$3:$F$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'03_CRM'!$A$3:$F$930</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'03_ERP'!$A$3:$F$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'03_GA4'!$A$3:$F$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'03_ERP'!$A$3:$F$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'03_GA4'!$A$3:$F$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BRONZE 노출감사 — 전 원천 1121컬럼 (2026-07-28)</t>
+          <t>BRONZE 노출감사 — 전 원천 1162컬럼 (2026-08-06)</t>
         </is>
       </c>
     </row>
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>8.4%</t>
         </is>
       </c>
     </row>
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -647,11 +647,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1.1%</t>
         </is>
       </c>
     </row>
@@ -662,11 +662,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>612</v>
+        <v>598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.4%</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1121</v>
+        <v>1162</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>7</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>591</v>
+        <v>549</v>
       </c>
       <c r="H19" t="n">
         <v>51</v>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -892,13 +892,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -921,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1018,20 +1018,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AGE_BAND</t>
+          <t>AGE_AT_EVENT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>104</v>
+        <v>253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as AGE_BAND</t>
+          <t>CAST(NULL AS NUMBER(2,0)) as AGE_AT_EVENT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1043,20 +1043,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMOUNT_BAND1</t>
+          <t>AGE_BAND_AT_EVENT</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>75</v>
+        <v>254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as AMOUNT_BAND1</t>
+          <t>CAST(NULL AS VARCHAR) as AGE_BAND_AT_EVENT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1073,15 +1073,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMOUNT_BAND2</t>
+          <t>AMOUNT_BAND1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>75</v>
+        <v>234</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as AMOUNT_BAND2</t>
+          <t>CAST(NULL AS VARCHAR) as AMOUNT_BAND1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1093,20 +1093,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FACT_TARGET_BIZ.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ANNUAL_CUM_GOAL_CNT</t>
+          <t>AMOUNT_BAND2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(18,4)) as ANNUAL_CUM_GOAL_CNT</t>
+          <t>CAST(NULL AS VARCHAR) as AMOUNT_BAND2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1118,20 +1118,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DIM_EVENT.sql</t>
+          <t>FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>APPLY_CHANNEL</t>
+          <t>ANNUAL_CUM_GOAL_CNT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as APPLY_CHANNEL</t>
+          <t>CAST(NULL AS NUMBER(18,4)) as ANNUAL_CUM_GOAL_CNT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1143,20 +1143,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.sql</t>
+          <t>DIM_EVENT.sql</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AVG_SESSION_DURATION</t>
+          <t>APPLY_CHANNEL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER) as AVG_SESSION_DURATION</t>
+          <t>CAST(NULL AS VARCHAR) as APPLY_CHANNEL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1168,20 +1168,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BOUNCE_RATE</t>
+          <t>AREA_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>255</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER) as BOUNCE_RATE</t>
+          <t>CAST(NULL AS VARCHAR) as AREA_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1193,57 +1193,57 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FACT_AD_PERFORMANCE.sql</t>
+          <t>FACT_GA_BEHAVIOR.sql</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CAMPAIGN_SK</t>
+          <t>AVG_SESSION_DURATION</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0 as CAMPAIGN_SK</t>
+          <t>CAST(NULL AS NUMBER) as AVG_SESSION_DURATION</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.sql, FACT_TARGET_BIZ.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.sql</t>
+          <t>FACT_GA_BEHAVIOR.sql</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CAMPAIGN_SK</t>
+          <t>BOUNCE_RATE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0 as CAMPAIGN_SK</t>
+          <t>CAST(NULL AS NUMBER) as BOUNCE_RATE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.sql, FACT_TARGET_BIZ.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.sql</t>
+          <t>FACT_AD_PERFORMANCE.sql</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1261,14 +1261,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.sql, FACT_TARGET_BIZ.sql</t>
+          <t>DIM_CAMPAIGN.sql, FACT_MEMBER_EVENT.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.sql</t>
+          <t>FACT_BUDGET.sql</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1286,14 +1286,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.sql, FACT_TARGET_BIZ.sql</t>
+          <t>DIM_CAMPAIGN.sql, FACT_MEMBER_EVENT.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_EVENT_PARTICIPATION.sql</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1311,14 +1311,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.sql, FACT_TARGET_BIZ.sql</t>
+          <t>DIM_CAMPAIGN.sql, FACT_MEMBER_EVENT.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_GA_BEHAVIOR.sql</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1336,14 +1336,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.sql, FACT_TARGET_BIZ.sql</t>
+          <t>DIM_CAMPAIGN.sql, FACT_MEMBER_EVENT.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1368,70 +1368,70 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_IDENTITY.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHILD_CODE</t>
+          <t>CAMPAIGN_SK</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as CHILD_CODE</t>
+          <t>0 as CAMPAIGN_SK</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_CAMPAIGN.sql, FACT_MEMBER_EVENT.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DIM_ORG.sql</t>
+          <t>FACT_SERVICE_EVENT.sql</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CORP</t>
+          <t>CAMPAIGN_SK</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as CORP</t>
+          <t>0 as CAMPAIGN_SK</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_CAMPAIGN.sql, FACT_MEMBER_EVENT.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.sql</t>
+          <t>DIM_MEMBER_IDENTITY.sql</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CURRENT_SPONSORSHIP</t>
+          <t>CHILD_CODE</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as CURRENT_SPONSORSHIP</t>
+          <t>CAST(NULL AS VARCHAR) as CHILD_CODE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1443,95 +1443,95 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FACT_AD_PERFORMANCE.sql</t>
+          <t>DIM_ORG.sql</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DEVICE_SK</t>
+          <t>CORP</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0 as DEVICE_SK</t>
+          <t>CAST(NULL AS VARCHAR) as CORP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>DIM_DEVICE.sql, FACT_GA_BEHAVIOR.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_AD_PERFORMANCE.sql</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DEV_TYPE</t>
+          <t>DEVICE_SK</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as DEV_TYPE</t>
+          <t>0 as DEVICE_SK</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FACT_TARGET_DEV.sql</t>
+          <t>DIM_DEVICE.sql, FACT_GA_BEHAVIOR.sql</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DIM_ORG.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DIVISION</t>
+          <t>DEV_TYPE</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as DIVISION</t>
+          <t>CAST(NULL AS VARCHAR) as DEV_TYPE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FACT_TARGET_DEV.sql, WIDE_DEV_ACHIEVEMENT.sql</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.sql</t>
+          <t>DIM_ORG.sql</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DOMESTIC_OVERSEAS</t>
+          <t>DIVISION</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as DOMESTIC_OVERSEAS</t>
+          <t>CAST(NULL AS VARCHAR) as DIVISION</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1543,45 +1543,45 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DIM_AD_CREATIVE.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DURATION_SEC</t>
+          <t>DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
+        <v>237</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(9,0)) as DURATION_SEC</t>
+          <t>CAST(NULL AS VARCHAR) as DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FACT_AD_BROADCAST.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EFFECTIVE_TO</t>
+          <t>DVLP_DIV_NM</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CAST(NULL AS DATE) as EFFECTIVE_TO</t>
+          <t>CAST(NULL AS VARCHAR) as DVLP_DIV_NM</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1593,20 +1593,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.sql</t>
+          <t>DIM_MEMBER.sql</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EXEC_BUDGET_EST</t>
+          <t>EFFECTIVE_TO</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(18,2)) as EXEC_BUDGET_EST</t>
+          <t>CAST(NULL AS DATE) as EFFECTIVE_TO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1618,20 +1618,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DIM_PAYMENT.sql</t>
+          <t>FACT_BUDGET.sql</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FEE_TYPE</t>
+          <t>EXEC_BUDGET_EST</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as FEE_TYPE</t>
+          <t>CAST(NULL AS NUMBER(18,2)) as EXEC_BUDGET_EST</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1643,20 +1643,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.sql</t>
+          <t>DIM_PAYMENT.sql</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FIRST_SPONSORSHIP</t>
+          <t>FEE_TYPE</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as FIRST_SPONSORSHIP</t>
+          <t>CAST(NULL AS VARCHAR) as FEE_TYPE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1693,20 +1693,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>INCREASE_FLAG</t>
+          <t>GENDER_AT_EVENT</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28</v>
+        <v>260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CAST(NULL AS BOOLEAN) as INCREASE_FLAG</t>
+          <t>CAST(NULL AS VARCHAR) as GENDER_AT_EVENT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1718,7 +1718,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_EVENT_PARTICIPATION.sql</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1743,20 +1743,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JOIN_DATE</t>
+          <t>INCREASE_FLAG</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>33</v>
+        <v>232</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CAST(NULL AS DATE) as JOIN_DATE</t>
+          <t>CAST(NULL AS BOOLEAN) as INCREASE_FLAG</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1768,7 +1768,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>74</v>
+        <v>242</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1786,52 +1786,52 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LAST_CAMPAIGN</t>
+          <t>JOIN_DATE</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>122</v>
+        <v>233</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as LAST_CAMPAIGN</t>
+          <t>CAST(NULL AS DATE) as JOIN_DATE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.sql</t>
+          <t>FACT_SERVICE_EVENT.sql</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LAST_STOP_DATE</t>
+          <t>MAIL_RECEIVE_FLAG</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CAST(NULL AS DATE) as LAST_STOP_DATE</t>
+          <t>CAST(NULL AS BOOLEAN) as MAIL_RECEIVE_FLAG</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1848,15 +1848,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MAIL_RECEIVE_FLAG</t>
+          <t>MEMBER_STOP_FLAG</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CAST(NULL AS BOOLEAN) as MAIL_RECEIVE_FLAG</t>
+          <t>CAST(NULL AS BOOLEAN) as MEMBER_STOP_FLAG</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1868,20 +1868,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.sql</t>
+          <t>DIM_MEMBER_IDENTITY.sql</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MEMBER_STOP_FLAG</t>
+          <t>MEMNUM</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CAST(NULL AS BOOLEAN) as MEMBER_STOP_FLAG</t>
+          <t>CAST(NULL AS VARCHAR) as MEMNUM</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1893,20 +1893,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_IDENTITY.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MEMNUM</t>
+          <t>NEW_EXISTING_FLAG</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>27</v>
+        <v>194</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as MEMNUM</t>
+          <t>CAST(NULL AS VARCHAR) as NEW_EXISTING_FLAG</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1918,7 +1918,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>115</v>
+        <v>237</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1943,20 +1943,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NEW_EXISTING_FLAG</t>
+          <t>NEW_FLAG</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as NEW_EXISTING_FLAG</t>
+          <t>CAST(NULL AS BOOLEAN) as NEW_FLAG</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1968,57 +1968,57 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>DIM_CAMPAIGN.sql</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NEW_EXISTING_FLAG</t>
+          <t>ORG_SK</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as NEW_EXISTING_FLAG</t>
+          <t>0 as ORG_SK</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_ORG.sql, FACT_MEMBER_EVENT.sql, FACT_TARGET_BIZ.sql, FACT_TARGET_DEV.sql, WIDE_DEV_ACHIEVEMENT.sql</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_BUDGET.sql</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NEW_FLAG</t>
+          <t>ORG_SK</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CAST(NULL AS BOOLEAN) as NEW_FLAG</t>
+          <t>0 as ORG_SK</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_ORG.sql, FACT_MEMBER_EVENT.sql, FACT_TARGET_BIZ.sql, FACT_TARGET_DEV.sql, WIDE_DEV_ACHIEVEMENT.sql</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>25</v>
+        <v>224</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2036,57 +2036,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>DIM_ORG.sql, FACT_TARGET_BIZ.sql, FACT_TARGET_DEV.sql</t>
+          <t>DIM_ORG.sql, FACT_TARGET_BIZ.sql, FACT_TARGET_DEV.sql, WIDE_DEV_ACHIEVEMENT.sql</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ORG_SK</t>
+          <t>PAYMENT_SK</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0 as ORG_SK</t>
+          <t>0 as PAYMENT_SK</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>DIM_ORG.sql, FACT_TARGET_BIZ.sql, FACT_TARGET_DEV.sql</t>
+          <t>DIM_PAYMENT.sql</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ORG_SK</t>
+          <t>PERIOD_BAND1</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>14</v>
+        <v>235</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0 as ORG_SK</t>
+          <t>CAST(NULL AS VARCHAR) as PERIOD_BAND1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>DIM_ORG.sql, FACT_TARGET_BIZ.sql, FACT_TARGET_DEV.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2098,40 +2098,40 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PAYMENT_SK</t>
+          <t>PERIOD_BAND2</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>58</v>
+        <v>235</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0 as PAYMENT_SK</t>
+          <t>CAST(NULL AS VARCHAR) as PERIOD_BAND2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>DIM_PAYMENT.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_BUDGET.sql</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PERIOD_BAND1</t>
+          <t>PLAN_BUDGET_YEAR</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as PERIOD_BAND1</t>
+          <t>CAST(NULL AS NUMBER(18,2)) as PLAN_BUDGET_YEAR</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2143,20 +2143,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>DIM_AD_CREATIVE.sql</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PERIOD_BAND2</t>
+          <t>PLATFORM_TYPE</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as PERIOD_BAND2</t>
+          <t>CAST(NULL AS VARCHAR) as PLATFORM_TYPE</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2168,145 +2168,145 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.sql</t>
+          <t>DIM_MEMBER.sql</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PLAN_BUDGET_YEAR</t>
+          <t>PREV_MBER_STAT_CD</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(18,2)) as PLAN_BUDGET_YEAR</t>
+          <t>CAST(NULL AS VARCHAR) as PREV_MBER_STAT_CD</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WIDE_MEMBER_EVENT.sql, WIDE_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DIM_AD_CREATIVE.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PLATFORM_TYPE</t>
+          <t>REASON_SK</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>22</v>
+        <v>178</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as PLATFORM_TYPE</t>
+          <t>0 as REASON_SK</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_REASON.sql, FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>REASON_SK</t>
+          <t>REDONATE_FLAG</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>14</v>
+        <v>232</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0 as REASON_SK</t>
+          <t>CAST(NULL AS BOOLEAN) as REDONATE_FLAG</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DIM_REASON.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>REASON_SK</t>
+          <t>REGION_AT_EVENT</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0 as REASON_SK</t>
+          <t>CAST(NULL AS VARCHAR) as REGION_AT_EVENT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DIM_REASON.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>DIM_AD_CREATIVE.sql</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>REDONATE_FLAG</t>
+          <t>RT_TYPE</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CAST(NULL AS BOOLEAN) as REDONATE_FLAG</t>
+          <t>CAST(NULL AS VARCHAR) as RT_TYPE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FACT_AD_BROADCAST.sql</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.sql</t>
+          <t>FACT_EVENT_PARTICIPATION.sql</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>REGION</t>
+          <t>SELF_PART_FLAG</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as REGION</t>
+          <t>CAST(NULL AS BOOLEAN) as SELF_PART_FLAG</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2318,45 +2318,45 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DIM_AD_CREATIVE.sql</t>
+          <t>FACT_SERVICE_EVENT.sql</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RT_TYPE</t>
+          <t>SEND_STATUS2</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as RT_TYPE</t>
+          <t>CAST(NULL AS VARCHAR) as SEND_STATUS2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FACT_AD_BROADCAST.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SELF_PART_FLAG</t>
+          <t>SEX_AT_EVENT</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>24</v>
+        <v>259</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CAST(NULL AS BOOLEAN) as SELF_PART_FLAG</t>
+          <t>CAST(NULL AS VARCHAR) as SEX_AT_EVENT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2368,20 +2368,20 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SEND_STATUS2</t>
+          <t>SPNSR_AMT</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>35</v>
+        <v>239</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SEND_STATUS2</t>
+          <t>CAST(NULL AS NUMBER(18,0)) as SPNSR_AMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2393,82 +2393,82 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DIM_SERVICE.sql</t>
+          <t>FACT_BUDGET.sql</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SEND_TYPE_L</t>
+          <t>SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SEND_TYPE_L</t>
+          <t>CAST(NULL AS NUMBER(38,0)) as SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_SPONSORSHIP.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DIM_SERVICE.sql</t>
+          <t>FACT_EVENT_PARTICIPATION.sql</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SEND_TYPE_M</t>
+          <t>SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SEND_TYPE_M</t>
+          <t>0 as SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_SPONSORSHIP.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DIM_SERVICE.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SEND_TYPE_S</t>
+          <t>SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SEND_TYPE_S</t>
+          <t>0 as SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_SPONSORSHIP.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2477,11 +2477,11 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(38,0)) as SPONSORSHIP_SK</t>
+          <t>0 as SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2493,25 +2493,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_SK</t>
+          <t>STOP_CHANNEL</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>18</v>
+        <v>190</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0 as SPONSORSHIP_SK</t>
+          <t>CAST(NULL AS VARCHAR) as STOP_CHANNEL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.sql, FACT_TARGET_BIZ.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2523,70 +2523,70 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_SK</t>
+          <t>STOP_CHANNEL_NM</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>14</v>
+        <v>193</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0 as SPONSORSHIP_SK</t>
+          <t>CAST(NULL AS VARCHAR) as STOP_CHANNEL_NM</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.sql, FACT_TARGET_BIZ.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_SK</t>
+          <t>STOP_DATE</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>58</v>
+        <v>188</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0 as SPONSORSHIP_SK</t>
+          <t>CAST(NULL AS DATE) as STOP_DATE</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.sql, FACT_TARGET_BIZ.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>STOP_DATE</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>233</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CAST(NULL AS DATE) as STOP_DATE</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>FACT_MEMBER_EVENT.sql</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>STOP_CHANNEL</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>20</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>CAST(NULL AS VARCHAR) as STOP_CHANNEL</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -2598,15 +2598,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>STOP_DATE</t>
+          <t>STOP_REASON</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CAST(NULL AS DATE) as STOP_DATE</t>
+          <t>CAST(NULL AS VARCHAR) as STOP_REASON</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2618,45 +2618,45 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>STOP_DATE</t>
+          <t>STOP_REASON_NM</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CAST(NULL AS DATE) as STOP_DATE</t>
+          <t>CAST(NULL AS VARCHAR) as STOP_REASON_NM</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>STOP_REASON</t>
+          <t>SUPP_CUM_GOAL_CNT</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as STOP_REASON</t>
+          <t>CAST(NULL AS NUMBER(18,4)) as SUPP_CUM_GOAL_CNT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2668,20 +2668,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FACT_TARGET_BIZ.sql</t>
+          <t>DIM_AD_CREATIVE.sql</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SUPP_CUM_GOAL_CNT</t>
+          <t>TARGET_GROUP</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(18,4)) as SUPP_CUM_GOAL_CNT</t>
+          <t>CAST(NULL AS VARCHAR) as TARGET_GROUP</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2693,48 +2693,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DIM_AD_CREATIVE.sql</t>
+          <t>DIM_ORG.sql</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TARGET_GROUP</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as TARGET_GROUP</t>
+          <t>CAST(NULL AS VARCHAR) as TEAM</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>DIM_ORG.sql</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>22</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>CAST(NULL AS VARCHAR) as TEAM</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4507,7 +4482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4521,7 +4496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AGENCY — 102컬럼</t>
+          <t>AGENCY — 106컬럼</t>
         </is>
       </c>
     </row>
@@ -6800,108 +6775,108 @@
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>VIDEO_AD_CMPGN_DTLS</t>
+          <t>SYNC_ERR_INFO</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>CHNNL_NM</t>
+          <t>ERR_SEQ</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D74" s="15" t="inlineStr">
-        <is>
-          <t>노출됨(GOLD)</t>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `CHANNEL_COMPANY` (FACT_AD_BROADCAST.sql)</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>VIDEO_AD_CMPGN_DTLS</t>
+          <t>SYNC_ERR_INFO</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>ERR_DATETIME</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D75" s="13" t="inlineStr">
-        <is>
-          <t>대체노출(파생)</t>
+          <t>TIMESTAMP_NTZ</t>
+        </is>
+      </c>
+      <c r="D75" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>DATE 파생(DAYNAME) 로 대체</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>VIDEO_AD_CMPGN_DTLS</t>
+          <t>SYNC_ERR_INFO</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>BRDC_DATE</t>
+          <t>DATA_TYPE</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
-        <is>
-          <t>노출됨(GOLD)</t>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `BROADCAST_DATE` (FACT_AD_BROADCAST.sql)</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>VIDEO_AD_CMPGN_DTLS</t>
+          <t>SYNC_ERR_INFO</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>TIME_RNG</t>
+          <t>ERR_INFO</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6909,19 +6884,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D77" s="15" t="inlineStr">
-        <is>
-          <t>노출됨(GOLD)</t>
+      <c r="D77" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `TIME_BAND` (FACT_AD_BROADCAST.sql)</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
@@ -6933,7 +6908,7 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DAY_DIV_NM</t>
+          <t>CHNNL_NM</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
@@ -6953,7 +6928,7 @@
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `DAY_DIV` (FACT_AD_BROADCAST.sql)</t>
+          <t>개명 적재 → GOLD `CHANNEL_COMPANY` (FACT_AD_BROADCAST.sql)</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6940,7 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>PRG_STRT_TIME</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -6973,9 +6948,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D79" s="15" t="inlineStr">
-        <is>
-          <t>노출됨(GOLD)</t>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>대체노출(파생)</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
@@ -6985,7 +6960,7 @@
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `PRG_START_TIME` (FACT_AD_BROADCAST.sql)</t>
+          <t>DATE 파생(DAYNAME) 로 대체</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6972,12 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>SCHDL_NM</t>
+          <t>BRDC_DATE</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
@@ -7017,7 +6992,7 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `PROGRAM_NM` (FACT_AD_BROADCAST.sql)</t>
+          <t>개명 적재 → GOLD `BROADCAST_DATE` (FACT_AD_BROADCAST.sql)</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7004,7 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>TIME_RNG</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -7037,19 +7012,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>판정보류(동명이의)</t>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>낮음(일반명 충돌)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>동명 GOLD/SILVER 컬럼이 있으나 계보 무관 가능 — 실측 필요(P14)</t>
+          <t>개명 적재 → GOLD `TIME_BAND` (FACT_AD_BROADCAST.sql)</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7036,7 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>CM_AREA</t>
+          <t>DAY_DIV_NM</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
@@ -7081,7 +7056,7 @@
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `CM_POSITION` (FACT_AD_BROADCAST.sql)</t>
+          <t>개명 적재 → GOLD `DAY_DIV` (FACT_AD_BROADCAST.sql)</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7068,7 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>AD_STRT_TIME</t>
+          <t>PRG_STRT_TIME</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -7113,7 +7088,7 @@
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `AD_START_TIME` (FACT_AD_BROADCAST.sql)</t>
+          <t>개명 적재 → GOLD `PRG_START_TIME` (FACT_AD_BROADCAST.sql)</t>
         </is>
       </c>
     </row>
@@ -7125,7 +7100,7 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>AD_END_TIME</t>
+          <t>SCHDL_NM</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
@@ -7145,7 +7120,7 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
+          <t>개명 적재 → GOLD `PROGRAM_NM` (FACT_AD_BROADCAST.sql)</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7132,7 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>SPOT_TY</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -7165,19 +7140,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D85" s="15" t="inlineStr">
-        <is>
-          <t>노출됨(GOLD)</t>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>판정보류(동명이의)</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음(일반명 충돌)</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `SPOT_TYPE` (FACT_AD_BROADCAST.sql)</t>
+          <t>동명 GOLD/SILVER 컬럼이 있으나 계보 무관 가능 — 실측 필요(P14)</t>
         </is>
       </c>
     </row>
@@ -7189,12 +7164,12 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>AD_VIEW_RT</t>
+          <t>CM_AREA</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
@@ -7209,7 +7184,7 @@
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `AD_VIEW_RT_SRC` (FACT_AD_BROADCAST.sql)</t>
+          <t>개명 적재 → GOLD `CM_POSITION` (FACT_AD_BROADCAST.sql)</t>
         </is>
       </c>
     </row>
@@ -7221,12 +7196,12 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>AD_CNT</t>
+          <t>AD_STRT_TIME</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D87" s="15" t="inlineStr">
@@ -7241,7 +7216,7 @@
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
+          <t>개명 적재 → GOLD `AD_START_TIME` (FACT_AD_BROADCAST.sql)</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7228,7 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>AD_SEC</t>
+          <t>AD_END_TIME</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
@@ -7273,7 +7248,7 @@
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `DURATION_SEC` (FACT_AD_BROADCAST.sql)</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -7285,12 +7260,12 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>ACTL_PUR_AD_COST_KRW</t>
+          <t>SPOT_TY</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D89" s="15" t="inlineStr">
@@ -7305,7 +7280,7 @@
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `AD_COST` (FACT_AD_PERFORMANCE.sql)</t>
+          <t>개명 적재 → GOLD `SPOT_TYPE` (FACT_AD_BROADCAST.sql)</t>
         </is>
       </c>
     </row>
@@ -7317,12 +7292,12 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>INBOUND_CALL_CNT</t>
+          <t>AD_VIEW_RT</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>FLOAT</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
@@ -7337,7 +7312,7 @@
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
+          <t>개명 적재 → GOLD `AD_VIEW_RT_SRC` (FACT_AD_BROADCAST.sql)</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7324,12 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>CPC</t>
+          <t>AD_CNT</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="D91" s="15" t="inlineStr">
@@ -7369,7 +7344,7 @@
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `CPC_SRC` (FACT_AD_BROADCAST.sql)</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7356,7 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>UPPER_CMPGN_NM</t>
+          <t>AD_SEC</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
@@ -7389,9 +7364,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D92" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -7401,7 +7376,7 @@
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명 적재 → GOLD `DURATION_SEC` (FACT_AD_BROADCAST.sql)</t>
         </is>
       </c>
     </row>
@@ -7413,17 +7388,17 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>MATR_NM</t>
+          <t>ACTL_PUR_AD_COST_KRW</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D93" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
@@ -7433,7 +7408,7 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명 적재 → GOLD `AD_COST` (FACT_AD_PERFORMANCE.sql)</t>
         </is>
       </c>
     </row>
@@ -7445,17 +7420,17 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>CMPGN_TY_NM</t>
+          <t>INBOUND_CALL_CNT</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D94" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
@@ -7465,7 +7440,7 @@
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -7477,7 +7452,7 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>DUR_PD_MATR_CHN</t>
+          <t>CPC</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
@@ -7485,9 +7460,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D95" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D95" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
@@ -7497,7 +7472,7 @@
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명 적재 → GOLD `CPC_SRC` (FACT_AD_BROADCAST.sql)</t>
         </is>
       </c>
     </row>
@@ -7509,7 +7484,7 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>CHNNL_CMPNY_TY_NM</t>
+          <t>UPPER_CMPGN_NM</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
@@ -7517,9 +7492,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D96" s="15" t="inlineStr">
-        <is>
-          <t>노출됨(GOLD)</t>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
@@ -7529,7 +7504,7 @@
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `CHANNEL_COMPANY_TYPE` (FACT_AD_BROADCAST.sql)</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7516,7 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>WEEK</t>
+          <t>MATR_NM</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7549,9 +7524,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D97" s="13" t="inlineStr">
-        <is>
-          <t>대체노출(파생)</t>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
@@ -7561,7 +7536,7 @@
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>DATE 파생(WEEKOFYEAR) 로 대체</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -7573,17 +7548,17 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>CONV_CALL_CNT</t>
+          <t>CMPGN_TY_NM</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="D98" s="15" t="inlineStr">
-        <is>
-          <t>노출됨(GOLD)</t>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
@@ -7593,7 +7568,7 @@
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `CONV_CALL_CNT` (FACT_AD_BROADCAST.sql)</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7580,7 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>BRDC_MT</t>
+          <t>DUR_PD_MATR_CHN</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -7613,9 +7588,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D99" s="13" t="inlineStr">
-        <is>
-          <t>대체노출(파생)</t>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
@@ -7625,7 +7600,7 @@
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>DATE 파생(MONTH) 로 대체</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -7637,7 +7612,7 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>YEAR</t>
+          <t>CHNNL_CMPNY_TY_NM</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
@@ -7645,9 +7620,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D100" s="13" t="inlineStr">
-        <is>
-          <t>대체노출(파생)</t>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
@@ -7657,7 +7632,7 @@
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>DATE 파생(YEAR(AD_DATE)) 로 대체 — 텍스트 파싱 금지 원칙</t>
+          <t>개명 적재 → GOLD `CHANNEL_COMPANY_TYPE` (FACT_AD_BROADCAST.sql)</t>
         </is>
       </c>
     </row>
@@ -7669,7 +7644,7 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>CTV_DIV_NM</t>
+          <t>WEEK</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
@@ -7677,9 +7652,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D101" s="15" t="inlineStr">
-        <is>
-          <t>노출됨(GOLD)</t>
+      <c r="D101" s="13" t="inlineStr">
+        <is>
+          <t>대체노출(파생)</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
@@ -7689,7 +7664,7 @@
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `CTV_DIV` (FACT_AD_BROADCAST.sql)</t>
+          <t>DATE 파생(WEEKOFYEAR) 로 대체</t>
         </is>
       </c>
     </row>
@@ -7701,17 +7676,17 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>MKT_CMPGN_NM</t>
+          <t>CONV_CALL_CNT</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D102" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
@@ -7721,7 +7696,7 @@
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명 적재 → GOLD `CONV_CALL_CNT` (FACT_AD_BROADCAST.sql)</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7708,7 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>SPNSR_BSNS_NM</t>
+          <t>BRDC_MT</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -7741,19 +7716,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D103" s="12" t="inlineStr">
-        <is>
-          <t>판정보류(동명이의)</t>
+      <c r="D103" s="13" t="inlineStr">
+        <is>
+          <t>대체노출(파생)</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>낮음(일반명 충돌)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>동명 GOLD/SILVER 컬럼이 있으나 계보 무관 가능 — 실측 필요(P14)</t>
+          <t>DATE 파생(MONTH) 로 대체</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7740,7 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>DMST_OVSEA_DIV_NM</t>
+          <t>YEAR</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
@@ -7773,9 +7748,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D104" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>대체노출(파생)</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
@@ -7785,7 +7760,7 @@
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>DATE 파생(YEAR(AD_DATE)) 로 대체 — 텍스트 파싱 금지 원칙</t>
         </is>
       </c>
     </row>
@@ -7797,32 +7772,160 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
+          <t>CTV_DIV_NM</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D105" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>개명 적재 → GOLD `CTV_DIV` (FACT_AD_BROADCAST.sql)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>MKT_CMPGN_NM</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>GOLD 미승격</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>SPNSR_BSNS_NM</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>판정보류(동명이의)</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>낮음(일반명 충돌)</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>동명 GOLD/SILVER 컬럼이 있으나 계보 무관 가능 — 실측 필요(P14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>DMST_OVSEA_DIV_NM</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D108" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>GOLD 미승격</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
           <t>BSNS_CASE_DIV_NM</t>
         </is>
       </c>
-      <c r="C105" s="11" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D105" s="14" t="inlineStr">
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D109" s="14" t="inlineStr">
         <is>
           <t>SILVER까지만</t>
         </is>
       </c>
-      <c r="E105" s="11" t="inlineStr">
+      <c r="E109" s="11" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="F105" s="11" t="inlineStr">
+      <c r="F109" s="11" t="inlineStr">
         <is>
           <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F105"/>
+  <autoFilter ref="A3:F109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8123,19 +8226,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>판정보류(동명이의)</t>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>낮음(일반명 충돌)</t>
+          <t>낮음(일반명)</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>동명 GOLD/SILVER 컬럼이 있으나 계보 무관 가능 — 실측 필요(P14)</t>
+          <t>일반명 — 개별 실측 필요</t>
         </is>
       </c>
     </row>
@@ -10363,9 +10466,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D81" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
@@ -10375,7 +10478,7 @@
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -10395,9 +10498,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D82" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
@@ -10407,7 +10510,7 @@
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -10427,9 +10530,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D83" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
@@ -10439,7 +10542,7 @@
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -15387,9 +15490,9 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D238" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D238" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E238" s="11" t="inlineStr">
@@ -15399,7 +15502,7 @@
       </c>
       <c r="F238" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -18331,19 +18434,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D330" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D330" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E330" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F330" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -18587,19 +18690,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D338" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D338" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E338" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F338" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -18651,19 +18754,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D340" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D340" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E340" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F340" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -18907,19 +19010,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D348" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D348" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E348" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F348" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -18939,19 +19042,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D349" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D349" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E349" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F349" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -19291,19 +19394,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D360" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D360" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E360" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F360" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -19355,19 +19458,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D362" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D362" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E362" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F362" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -20155,19 +20258,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D387" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D387" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E387" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F387" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -20827,19 +20930,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D408" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D408" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E408" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F408" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -21211,9 +21314,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D420" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D420" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E420" s="11" t="inlineStr">
@@ -21223,7 +21326,7 @@
       </c>
       <c r="F420" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -21403,9 +21506,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D426" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D426" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E426" s="11" t="inlineStr">
@@ -21415,7 +21518,7 @@
       </c>
       <c r="F426" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -22939,9 +23042,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D474" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D474" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E474" s="11" t="inlineStr">
@@ -22951,7 +23054,7 @@
       </c>
       <c r="F474" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -22971,9 +23074,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D475" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D475" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E475" s="11" t="inlineStr">
@@ -22983,7 +23086,7 @@
       </c>
       <c r="F475" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -23003,9 +23106,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D476" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D476" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E476" s="11" t="inlineStr">
@@ -23015,7 +23118,7 @@
       </c>
       <c r="F476" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -23099,19 +23202,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D479" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D479" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E479" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F479" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -23163,19 +23266,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D481" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D481" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E481" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F481" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -23195,19 +23298,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D482" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D482" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E482" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(모델별 상이)</t>
         </is>
       </c>
       <c r="F482" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>실적재 FACT_MEMBER_EVENT.sql / 하드코딩 FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
     </row>
@@ -23227,19 +23330,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D483" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D483" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E483" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(모델별 상이)</t>
         </is>
       </c>
       <c r="F483" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>실적재 FACT_MEMBER_EVENT.sql / 하드코딩 FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
     </row>
@@ -23419,9 +23522,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D489" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D489" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E489" s="11" t="inlineStr">
@@ -23431,7 +23534,7 @@
       </c>
       <c r="F489" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -23483,19 +23586,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D491" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D491" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E491" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F491" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -23515,19 +23618,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D492" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D492" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E492" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F492" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -23547,19 +23650,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D493" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D493" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E493" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F493" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -23579,19 +23682,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D494" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D494" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E494" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F494" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -23611,19 +23714,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D495" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D495" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E495" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F495" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -23643,19 +23746,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D496" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D496" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E496" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F496" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -23675,19 +23778,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D497" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D497" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E497" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F497" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -23963,9 +24066,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D506" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D506" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E506" s="11" t="inlineStr">
@@ -23975,7 +24078,7 @@
       </c>
       <c r="F506" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -23995,19 +24098,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D507" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D507" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E507" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F507" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -24091,9 +24194,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D510" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D510" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E510" s="11" t="inlineStr">
@@ -24103,7 +24206,7 @@
       </c>
       <c r="F510" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -24283,9 +24386,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D516" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D516" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E516" s="11" t="inlineStr">
@@ -24295,7 +24398,7 @@
       </c>
       <c r="F516" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -24539,19 +24642,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D524" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D524" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E524" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(모델별 상이)</t>
         </is>
       </c>
       <c r="F524" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>실적재 FACT_MEMBER_EVENT.sql / 하드코딩 FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
     </row>
@@ -24603,9 +24706,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D526" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D526" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E526" s="11" t="inlineStr">
@@ -24615,7 +24718,7 @@
       </c>
       <c r="F526" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -24635,9 +24738,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D527" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D527" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E527" s="11" t="inlineStr">
@@ -24647,7 +24750,7 @@
       </c>
       <c r="F527" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -24667,9 +24770,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D528" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D528" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E528" s="11" t="inlineStr">
@@ -24679,7 +24782,7 @@
       </c>
       <c r="F528" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -24763,19 +24866,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D531" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D531" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E531" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F531" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -25243,19 +25346,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D546" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D546" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E546" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(모델별 상이)</t>
         </is>
       </c>
       <c r="F546" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>실적재 FACT_MEMBER_EVENT.sql / 하드코딩 FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
     </row>
@@ -25755,9 +25858,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D562" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D562" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E562" s="11" t="inlineStr">
@@ -25767,7 +25870,7 @@
       </c>
       <c r="F562" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -25819,9 +25922,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D564" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D564" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E564" s="11" t="inlineStr">
@@ -25831,7 +25934,7 @@
       </c>
       <c r="F564" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -25851,19 +25954,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D565" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D565" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E565" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F565" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -25883,19 +25986,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D566" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D566" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E566" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F566" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -25915,19 +26018,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D567" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D567" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E567" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F567" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -29147,19 +29250,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D668" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D668" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E668" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F668" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -29179,19 +29282,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D669" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D669" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E669" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F669" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -29883,19 +29986,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D691" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D691" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E691" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F691" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -30651,19 +30754,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D715" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D715" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E715" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F715" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -30811,19 +30914,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D720" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D720" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E720" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F720" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -31163,9 +31266,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D731" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D731" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E731" s="11" t="inlineStr">
@@ -31175,7 +31278,7 @@
       </c>
       <c r="F731" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -31547,19 +31650,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D743" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D743" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E743" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F743" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -31867,19 +31970,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D753" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D753" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E753" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F753" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -32059,19 +32162,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D759" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D759" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E759" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F759" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -32347,19 +32450,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D768" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D768" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E768" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F768" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -32379,19 +32482,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D769" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D769" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E769" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F769" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -32603,19 +32706,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D776" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D776" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E776" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F776" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -32795,19 +32898,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D782" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D782" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E782" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F782" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -33179,19 +33282,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D794" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D794" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E794" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F794" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -33467,19 +33570,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D803" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D803" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E803" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F803" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -33531,19 +33634,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D805" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D805" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E805" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F805" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -33755,19 +33858,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D812" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D812" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E812" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F812" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -33787,19 +33890,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D813" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D813" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E813" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F813" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -34171,19 +34274,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D825" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D825" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E825" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F825" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -34235,19 +34338,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D827" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D827" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E827" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F827" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -35323,9 +35426,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D861" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D861" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E861" s="11" t="inlineStr">
@@ -35335,7 +35438,7 @@
       </c>
       <c r="F861" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -37371,19 +37474,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D925" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D925" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E925" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F925" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -37559,7 +37662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -37573,7 +37676,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ERP — 62컬럼</t>
+          <t>ERP — 64컬럼</t>
         </is>
       </c>
     </row>
@@ -37937,12 +38040,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>YEAR_BDGT_TOT_AMT</t>
+          <t>BDGT_ITEM_NM</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
@@ -37969,12 +38072,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>CHN_BDGT_TOT_AMT</t>
+          <t>DVLP_INBOUND_PATH</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
@@ -38001,7 +38104,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>ADJ_BDGT_TOT_AMT</t>
+          <t>YEAR_BDGT_TOT_AMT</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -38033,7 +38136,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>EXEC_TOT_AMT</t>
+          <t>CHN_BDGT_TOT_AMT</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -38065,7 +38168,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>YEAR_BDGT_AMT_1</t>
+          <t>ADJ_BDGT_TOT_AMT</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -38073,19 +38176,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>중간(SQL참조)</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>SILVER SQL 토큰 참조</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
@@ -38097,7 +38200,7 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>CHN_BDGT_AMT_1</t>
+          <t>EXEC_TOT_AMT</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -38105,19 +38208,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>중간(SQL참조)</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>SILVER SQL 토큰 참조</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
@@ -38129,7 +38232,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>ADJ_BDGT_AMT_1</t>
+          <t>YEAR_BDGT_AMT_1</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -38161,7 +38264,7 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>EXEC_AMT_1</t>
+          <t>CHN_BDGT_AMT_1</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -38193,7 +38296,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>YEAR_BDGT_AMT_2</t>
+          <t>ADJ_BDGT_AMT_1</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -38225,7 +38328,7 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>CHN_BDGT_AMT_2</t>
+          <t>EXEC_AMT_1</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -38257,7 +38360,7 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>ADJ_BDGT_AMT_2</t>
+          <t>YEAR_BDGT_AMT_2</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -38289,7 +38392,7 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>EXEC_AMT_2</t>
+          <t>CHN_BDGT_AMT_2</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -38321,7 +38424,7 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>YEAR_BDGT_AMT_3</t>
+          <t>ADJ_BDGT_AMT_2</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -38353,7 +38456,7 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>CHN_BDGT_AMT_3</t>
+          <t>EXEC_AMT_2</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -38385,7 +38488,7 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>ADJ_BDGT_AMT_3</t>
+          <t>YEAR_BDGT_AMT_3</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -38417,7 +38520,7 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>EXEC_AMT_3</t>
+          <t>CHN_BDGT_AMT_3</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -38449,7 +38552,7 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>YEAR_BDGT_AMT_4</t>
+          <t>ADJ_BDGT_AMT_3</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -38481,7 +38584,7 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>CHN_BDGT_AMT_4</t>
+          <t>EXEC_AMT_3</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -38513,7 +38616,7 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>ADJ_BDGT_AMT_4</t>
+          <t>YEAR_BDGT_AMT_4</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
@@ -38545,7 +38648,7 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>EXEC_AMT_4</t>
+          <t>CHN_BDGT_AMT_4</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
@@ -38577,7 +38680,7 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>YEAR_BDGT_AMT_5</t>
+          <t>ADJ_BDGT_AMT_4</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
@@ -38609,7 +38712,7 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>CHN_BDGT_AMT_5</t>
+          <t>EXEC_AMT_4</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -38641,7 +38744,7 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>ADJ_BDGT_AMT_5</t>
+          <t>YEAR_BDGT_AMT_5</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
@@ -38673,7 +38776,7 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>EXEC_AMT_5</t>
+          <t>CHN_BDGT_AMT_5</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -38705,7 +38808,7 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>YEAR_BDGT_AMT_6</t>
+          <t>ADJ_BDGT_AMT_5</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
@@ -38737,7 +38840,7 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>CHN_BDGT_AMT_6</t>
+          <t>EXEC_AMT_5</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -38769,7 +38872,7 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>ADJ_BDGT_AMT_6</t>
+          <t>YEAR_BDGT_AMT_6</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -38801,7 +38904,7 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>EXEC_AMT_6</t>
+          <t>CHN_BDGT_AMT_6</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -38833,7 +38936,7 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>YEAR_BDGT_AMT_7</t>
+          <t>ADJ_BDGT_AMT_6</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -38865,7 +38968,7 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>CHN_BDGT_AMT_7</t>
+          <t>EXEC_AMT_6</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -38897,7 +39000,7 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>ADJ_BDGT_AMT_7</t>
+          <t>YEAR_BDGT_AMT_7</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
@@ -38929,7 +39032,7 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>EXEC_AMT_7</t>
+          <t>CHN_BDGT_AMT_7</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -38961,7 +39064,7 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>YEAR_BDGT_AMT_8</t>
+          <t>ADJ_BDGT_AMT_7</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -38993,7 +39096,7 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>CHN_BDGT_AMT_8</t>
+          <t>EXEC_AMT_7</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -39025,7 +39128,7 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>ADJ_BDGT_AMT_8</t>
+          <t>YEAR_BDGT_AMT_8</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
@@ -39057,7 +39160,7 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>EXEC_AMT_8</t>
+          <t>CHN_BDGT_AMT_8</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -39089,7 +39192,7 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>YEAR_BDGT_AMT_9</t>
+          <t>ADJ_BDGT_AMT_8</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -39121,7 +39224,7 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>CHN_BDGT_AMT_9</t>
+          <t>EXEC_AMT_8</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -39153,7 +39256,7 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>ADJ_BDGT_AMT_9</t>
+          <t>YEAR_BDGT_AMT_9</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
@@ -39185,7 +39288,7 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>EXEC_AMT_9</t>
+          <t>CHN_BDGT_AMT_9</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -39217,7 +39320,7 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>YEAR_BDGT_AMT_10</t>
+          <t>ADJ_BDGT_AMT_9</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
@@ -39249,7 +39352,7 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>CHN_BDGT_AMT_10</t>
+          <t>EXEC_AMT_9</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -39281,7 +39384,7 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>ADJ_BDGT_AMT_10</t>
+          <t>YEAR_BDGT_AMT_10</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
@@ -39313,7 +39416,7 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>EXEC_AMT_10</t>
+          <t>CHN_BDGT_AMT_10</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -39345,7 +39448,7 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>YEAR_BDGT_AMT_11</t>
+          <t>ADJ_BDGT_AMT_10</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
@@ -39377,7 +39480,7 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>CHN_BDGT_AMT_11</t>
+          <t>EXEC_AMT_10</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -39409,7 +39512,7 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>ADJ_BDGT_AMT_11</t>
+          <t>YEAR_BDGT_AMT_11</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
@@ -39441,7 +39544,7 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>EXEC_AMT_11</t>
+          <t>CHN_BDGT_AMT_11</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -39473,7 +39576,7 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>YEAR_BDGT_AMT_12</t>
+          <t>ADJ_BDGT_AMT_11</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
@@ -39505,7 +39608,7 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>CHN_BDGT_AMT_12</t>
+          <t>EXEC_AMT_11</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -39537,7 +39640,7 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>ADJ_BDGT_AMT_12</t>
+          <t>YEAR_BDGT_AMT_12</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
@@ -39569,32 +39672,96 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
+          <t>CHN_BDGT_AMT_12</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>중간(SQL참조)</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>SILVER SQL 토큰 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>BDGT_ACMSLT_LEDGER</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>ADJ_BDGT_AMT_12</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>중간(SQL참조)</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>SILVER SQL 토큰 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>BDGT_ACMSLT_LEDGER</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
           <t>EXEC_AMT_12</t>
         </is>
       </c>
-      <c r="C65" s="11" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D65" s="14" t="inlineStr">
+      <c r="D67" s="14" t="inlineStr">
         <is>
           <t>SILVER까지만</t>
         </is>
       </c>
-      <c r="E65" s="11" t="inlineStr">
+      <c r="E67" s="11" t="inlineStr">
         <is>
           <t>중간(SQL참조)</t>
         </is>
       </c>
-      <c r="F65" s="11" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F65"/>
+  <autoFilter ref="A3:F67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39605,7 +39772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -39619,7 +39786,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GA4 — 30컬럼</t>
+          <t>GA4 — 65컬럼</t>
         </is>
       </c>
     </row>
@@ -39658,76 +39825,76 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>events_20260501</t>
+          <t>SYNC_ERR_INFO</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>ERR_SEQ</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>events_20260501</t>
+          <t>SYNC_ERR_INFO</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>event_timestamp</t>
+          <t>ERR_DATETIME</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+          <t>TIMESTAMP_NTZ</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>events_20260501</t>
+          <t>SYNC_ERR_INFO</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>event_name</t>
+          <t>DATA_TYPE</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -39735,51 +39902,51 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>노출됨(GOLD)</t>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `GA_EVENT_SK` (FACT_GA_BEHAVIOR.sql)</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>events_20260501</t>
+          <t>SYNC_ERR_INFO</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>event_params</t>
+          <t>ERR_INFO</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>VARIANT</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>중간(SQL참조)</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>SILVER SQL 토큰 참조</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
@@ -39791,27 +39958,27 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>event_previous_timestamp</t>
+          <t>event_date</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -39823,27 +39990,27 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>event_value_in_usd</t>
+          <t>event_timestamp</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -39855,27 +40022,27 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>event_bundle_sequence_id</t>
+          <t>event_name</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>개명 적재 → GOLD `GA_EVENT_SK` (FACT_GA_BEHAVIOR.sql)</t>
         </is>
       </c>
     </row>
@@ -39887,27 +40054,27 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>event_server_timestamp_offset</t>
+          <t>event_params</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -39919,27 +40086,27 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>event_previous_timestamp</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
@@ -39951,27 +40118,27 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>user_pseudo_id</t>
+          <t>event_value_in_usd</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
@@ -39983,12 +40150,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>privacy_info</t>
+          <t>event_bundle_sequence_id</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>VARIANT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
@@ -40015,12 +40182,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>user_properties</t>
+          <t>event_server_timestamp_offset</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>VARIANT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
@@ -40047,27 +40214,27 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>user_first_touch_timestamp</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -40079,27 +40246,27 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>user_ltv</t>
+          <t>user_pseudo_id</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>VARIANT</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -40111,7 +40278,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>privacy_info</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -40119,19 +40286,19 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>노출됨(GOLD)</t>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `DEVICE_SK` (FACT_GA_BEHAVIOR.sql)</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
@@ -40143,7 +40310,7 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>user_properties</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -40151,19 +40318,19 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>중간(SQL참조)</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>SILVER SQL 토큰 참조</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
@@ -40175,7 +40342,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>app_info</t>
+          <t>user_first_touch_timestamp</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -40207,7 +40374,7 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>traffic_source</t>
+          <t>user_ltv</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -40215,19 +40382,19 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>노출됨(GOLD)</t>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `GA_SOURCE_SK` (FACT_GA_BEHAVIOR.sql)</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
@@ -40239,27 +40406,27 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>stream_id</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>개명 적재 → GOLD `DEVICE_SK` (FACT_GA_BEHAVIOR.sql)</t>
         </is>
       </c>
     </row>
@@ -40271,27 +40438,27 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>geo</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>노출됨(GOLD)</t>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `DEVICE_SK` (FACT_GA_BEHAVIOR.sql)</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -40303,7 +40470,7 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>event_dimensions</t>
+          <t>app_info</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -40335,7 +40502,7 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>ecommerce</t>
+          <t>traffic_source</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -40343,19 +40510,19 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>개명 적재 → GOLD `GA_SOURCE_SK` (FACT_GA_BEHAVIOR.sql)</t>
         </is>
       </c>
     </row>
@@ -40367,12 +40534,12 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>stream_id</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>VARIANT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
@@ -40399,27 +40566,27 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>collected_traffic_source</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>VARIANT</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>개명 적재 → GOLD `DEVICE_SK` (FACT_GA_BEHAVIOR.sql)</t>
         </is>
       </c>
     </row>
@@ -40431,27 +40598,27 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>is_active_user</t>
+          <t>event_dimensions</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
@@ -40463,12 +40630,12 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>batch_event_index</t>
+          <t>ecommerce</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARIANT</t>
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr">
@@ -40495,12 +40662,12 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>batch_page_id</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARIANT</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
@@ -40527,27 +40694,27 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>batch_ordering_id</t>
+          <t>collected_traffic_source</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음(이름기반·P13)</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
@@ -40559,12 +40726,12 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>session_traffic_source_last_click</t>
+          <t>is_active_user</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>VARIANT</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
@@ -40574,12 +40741,12 @@
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>중간(SQL참조)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>SILVER SQL 토큰 참조</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -40591,32 +40758,1152 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
+          <t>batch_event_index</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>events_20260501</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>batch_page_id</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>events_20260501</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>batch_ordering_id</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>GOLD 미승격</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>events_20260501</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>session_traffic_source_last_click</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>중간(SQL참조)</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>SILVER SQL 토큰 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>events_20260501</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
           <t>publisher</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>낮음(이름기반·P13)</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>event_date</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>GOLD 미승격</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>event_timestamp</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>GOLD 미승격</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>event_name</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>개명 적재 → GOLD `GA_EVENT_SK` (FACT_GA_BEHAVIOR.sql)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>event_params</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>중간(SQL참조)</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>SILVER SQL 토큰 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>event_previous_timestamp</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>event_value_in_usd</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>event_bundle_sequence_id</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>event_server_timestamp_offset</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>GOLD 미승격</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>user_pseudo_id</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>GOLD 미승격</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>privacy_info</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>user_properties</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>user_first_touch_timestamp</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>user_ltv</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>개명 적재 → GOLD `DEVICE_SK` (FACT_GA_BEHAVIOR.sql)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>중간(SQL참조)</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>SILVER SQL 토큰 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>app_info</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>traffic_source</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>개명 적재 → GOLD `GA_SOURCE_SK` (FACT_GA_BEHAVIOR.sql)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>stream_id</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>개명 적재 → GOLD `DEVICE_SK` (FACT_GA_BEHAVIOR.sql)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>event_dimensions</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>ecommerce</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>items</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>collected_traffic_source</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D61" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>is_active_user</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>GOLD 미승격</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>batch_event_index</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>batch_page_id</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>batch_ordering_id</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>GOLD 미승격</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>session_traffic_source_last_click</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>VARIANT</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>중간(SQL참조)</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>SILVER SQL 토큰 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>events_20260719</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>event_original_occurrence_timestamp</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>미노출(검토대상)</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>낮음(이름기반·P13)</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
         <is>
           <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F33"/>
+  <autoFilter ref="A3:F68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/30_output_share/06_BRONZE노출감사.xlsx
+++ b/30_output_share/06_BRONZE노출감사.xlsx
@@ -124,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -151,9 +151,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -545,7 +542,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BRONZE 노출감사 — 전 원천 1162컬럼 (2026-08-06)</t>
+          <t>BRONZE 노출감사 — 전 원천 1162컬럼 (2026-08-07)</t>
         </is>
       </c>
     </row>
@@ -587,11 +584,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -617,11 +614,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -632,11 +629,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.7%</t>
         </is>
       </c>
     </row>
@@ -662,11 +659,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>50.6%</t>
         </is>
       </c>
     </row>
@@ -781,13 +778,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" t="n">
         <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>18</v>
@@ -815,7 +812,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -824,13 +821,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="F19" t="n">
         <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="H19" t="n">
         <v>51</v>
@@ -1002,7 +999,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1024,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1049,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1174,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1252,7 +1249,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1352,7 +1349,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1552,7 +1549,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1577,7 +1574,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1702,7 +1699,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1777,7 +1774,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1902,7 +1899,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2027,7 +2024,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2061,7 +2058,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>DIM_PAYMENT.sql</t>
+          <t>DIM_PAYMENT.sql, FACT_MEMBER_FEE.sql</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2199,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2252,7 +2249,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2352,7 +2349,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2377,7 +2374,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2411,7 +2408,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.sql, FACT_TARGET_BIZ.sql</t>
+          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2433,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.sql, FACT_TARGET_BIZ.sql</t>
+          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2449,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>174</v>
+        <v>232</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2461,7 +2458,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.sql, FACT_TARGET_BIZ.sql</t>
+          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_FEE.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2483,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.sql, FACT_TARGET_BIZ.sql</t>
+          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2499,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2527,7 +2524,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2552,7 +2549,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2602,7 +2599,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2627,7 +2624,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2726,7 +2723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3934,22 +3931,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VIDEO_AD_CMPGN_DTLS</t>
+          <t>TM_CM_CMPGN_MNG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ACTL_PUR_AD_COST_KRW</t>
+          <t>MKTG_CMPGN_NM</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AD_COST</t>
+          <t>MKTG_CAMPAIGN_SK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FACT_AD_PERFORMANCE.sql</t>
+          <t>DIM_CAMPAIGN.sql</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3961,22 +3958,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>VIDEO_AD_CMPGN_DTLS</t>
+          <t>TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AD_SEC</t>
+          <t>MK_CMPGN_CD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DURATION_SEC</t>
+          <t>MKTG_CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FACT_AD_BROADCAST.sql</t>
+          <t>DIM_MARKETING_CAMPAIGN.sql</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3988,22 +3985,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>VIDEO_AD_CMPGN_DTLS</t>
+          <t>TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AD_STRT_TIME</t>
+          <t>MK_CMPGN_NM</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AD_START_TIME</t>
+          <t>MKTG_CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FACT_AD_BROADCAST.sql</t>
+          <t>DIM_MARKETING_CAMPAIGN.sql</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4015,22 +4012,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>VIDEO_AD_CMPGN_DTLS</t>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AD_VIEW_RT</t>
+          <t>SPNSR_BSNS_ID</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AD_VIEW_RT_SRC</t>
+          <t>SPONSORSHIP_BK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FACT_AD_BROADCAST.sql</t>
+          <t>DIM_SPONSORSHIP.sql</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4042,76 +4039,76 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>VIDEO_AD_CMPGN_DTLS</t>
+          <t>TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BRDC_DATE</t>
+          <t>ACMSLT_DEPT_CD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BROADCAST_DATE</t>
+          <t>ORG_SK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FACT_AD_BROADCAST.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>✅ 적재</t>
+          <t>⚠️ 하드코딩 — 배선 필요</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>VIDEO_AD_CMPGN_DTLS</t>
+          <t>TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CHNNL_CMPNY_TY_NM</t>
+          <t>SPNSR_BSNS_ID</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CHANNEL_COMPANY_TYPE</t>
+          <t>SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FACT_AD_BROADCAST.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>✅ 적재</t>
+          <t>⚠️ 하드코딩 — 배선 필요</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VIDEO_AD_CMPGN_DTLS</t>
+          <t>TM_PM_DNTN_DTLS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CHNNL_NM</t>
+          <t>SPNSR_BSNS_ID</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CHANNEL_COMPANY</t>
+          <t>SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FACT_AD_BROADCAST.sql</t>
+          <t>FACT_MEMBER_FEE.sql</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4123,22 +4120,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>VIDEO_AD_CMPGN_DTLS</t>
+          <t>TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CM_AREA</t>
+          <t>MBRFEE_DIV_CD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CM_POSITION</t>
+          <t>FEE_DIV_CD</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FACT_AD_BROADCAST.sql</t>
+          <t>FACT_MEMBER_FEE.sql</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4150,22 +4147,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VIDEO_AD_CMPGN_DTLS</t>
+          <t>TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CONV_CALL_CNT</t>
+          <t>SPNSR_BSNS_ID</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CONV_CALL_CNT</t>
+          <t>SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FACT_AD_BROADCAST.sql</t>
+          <t>FACT_MEMBER_FEE.sql</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4182,17 +4179,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CPC</t>
+          <t>ACTL_PUR_AD_COST_KRW</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CPC_SRC</t>
+          <t>AD_COST</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>FACT_AD_BROADCAST.sql</t>
+          <t>FACT_AD_PERFORMANCE.sql</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4209,12 +4206,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CTV_DIV_NM</t>
+          <t>AD_SEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CTV_DIV</t>
+          <t>DURATION_SEC</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4236,12 +4233,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DAY_DIV_NM</t>
+          <t>AD_STRT_TIME</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DAY_DIV</t>
+          <t>AD_START_TIME</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4263,12 +4260,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PRG_STRT_TIME</t>
+          <t>AD_VIEW_RT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PRG_START_TIME</t>
+          <t>AD_VIEW_RT_SRC</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4290,12 +4287,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SCHDL_NM</t>
+          <t>BRDC_DATE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PROGRAM_NM</t>
+          <t>BROADCAST_DATE</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4317,12 +4314,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SPOT_TY</t>
+          <t>CHNNL_CMPNY_TY_NM</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SPOT_TYPE</t>
+          <t>CHANNEL_COMPANY_TYPE</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4344,12 +4341,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TIME_RNG</t>
+          <t>CHNNL_NM</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TIME_BAND</t>
+          <t>CHANNEL_COMPANY</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4366,22 +4363,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>events_</t>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>CM_AREA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DEVICE_SK</t>
+          <t>CM_POSITION</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.sql</t>
+          <t>FACT_AD_BROADCAST.sql</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4393,22 +4390,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>events_</t>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>event_name</t>
+          <t>CONV_CALL_CNT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GA_EVENT_SK</t>
+          <t>CONV_CALL_CNT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.sql</t>
+          <t>FACT_AD_BROADCAST.sql</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4420,22 +4417,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>events_</t>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>CPC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DEVICE_SK</t>
+          <t>CPC_SRC</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.sql</t>
+          <t>FACT_AD_BROADCAST.sql</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4447,25 +4444,268 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CTV_DIV_NM</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CTV_DIV</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.sql</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>✅ 적재</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>DAY_DIV_NM</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DAY_DIV</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.sql</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>✅ 적재</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PRG_STRT_TIME</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PRG_START_TIME</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.sql</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>✅ 적재</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SCHDL_NM</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PROGRAM_NM</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.sql</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>✅ 적재</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SPOT_TY</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SPOT_TYPE</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.sql</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>✅ 적재</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TIME_RNG</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>TIME_BAND</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.sql</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>✅ 적재</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>events_</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DEVICE_SK</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>FACT_GA_BEHAVIOR.sql</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>✅ 적재</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>events_</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>event_name</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>GA_EVENT_SK</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>FACT_GA_BEHAVIOR.sql</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>✅ 적재</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>events_</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>DEVICE_SK</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>FACT_GA_BEHAVIOR.sql</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>✅ 적재</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>events_</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
         <is>
           <t>traffic_source</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>GA_SOURCE_SK</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>FACT_GA_BEHAVIOR.sql</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>✅ 적재</t>
         </is>
@@ -4804,19 +5044,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>⚠️설계O·값미주입</t>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(브랜치별 상이)</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>GOLD `DEVICE_SK`(FACT_AD_PERFORMANCE.sql) 자리 존재하나 하드코딩 — FACT_AD_PERFORMANCE.sql:8 `0 as DEVICE_SK`</t>
+          <t>개명 적재 → GOLD `DEVICE_SK` (FACT_AD_PERFORMANCE.sql) · ⚠️ 일부 브랜치는 센티넬 — FACT_AD_PERFORMANCE.sql:8 `0 as DEVICE_SK`</t>
         </is>
       </c>
     </row>
@@ -6788,7 +7028,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D74" s="17" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -6820,7 +7060,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D75" s="17" t="inlineStr">
+      <c r="D75" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -6852,7 +7092,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D76" s="17" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -6884,7 +7124,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D77" s="17" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -8098,7 +8338,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -8130,7 +8370,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -8226,7 +8466,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -8290,9 +8530,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -8302,7 +8542,7 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8690,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -8482,7 +8722,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -8514,7 +8754,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -8546,7 +8786,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -8642,7 +8882,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -8674,7 +8914,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -8738,7 +8978,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -8770,7 +9010,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -8802,7 +9042,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -8866,7 +9106,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -8898,7 +9138,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -8962,7 +9202,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D34" s="18" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -8994,7 +9234,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D35" s="18" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -9058,7 +9298,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9090,7 +9330,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9154,7 +9394,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9186,7 +9426,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9218,7 +9458,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9250,7 +9490,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9282,7 +9522,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9314,7 +9554,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D45" s="18" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -9346,7 +9586,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9378,7 +9618,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9410,7 +9650,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9442,7 +9682,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D49" s="17" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9474,7 +9714,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9506,7 +9746,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D51" s="17" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9538,7 +9778,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D52" s="17" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9570,7 +9810,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9602,7 +9842,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D54" s="17" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9634,7 +9874,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D55" s="17" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9666,7 +9906,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D56" s="17" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9698,7 +9938,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9730,7 +9970,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9762,7 +10002,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="D59" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9794,7 +10034,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D60" s="17" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9858,7 +10098,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D62" s="17" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9890,7 +10130,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D63" s="17" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9922,7 +10162,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9954,7 +10194,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D65" s="17" t="inlineStr">
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -9986,7 +10226,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="D66" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10018,7 +10258,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10050,7 +10290,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10082,7 +10322,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D69" s="17" t="inlineStr">
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10114,7 +10354,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D70" s="17" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10146,7 +10386,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D71" s="17" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10178,7 +10418,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D72" s="17" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10210,7 +10450,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D73" s="17" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10242,7 +10482,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D74" s="17" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10274,7 +10514,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D75" s="17" t="inlineStr">
+      <c r="D75" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10306,7 +10546,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D76" s="17" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10338,7 +10578,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D77" s="17" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10370,7 +10610,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D78" s="17" t="inlineStr">
+      <c r="D78" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10402,7 +10642,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D79" s="17" t="inlineStr">
+      <c r="D79" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10594,7 +10834,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D85" s="17" t="inlineStr">
+      <c r="D85" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10626,7 +10866,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D86" s="17" t="inlineStr">
+      <c r="D86" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10658,7 +10898,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D87" s="17" t="inlineStr">
+      <c r="D87" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10690,7 +10930,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D88" s="17" t="inlineStr">
+      <c r="D88" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10722,7 +10962,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D89" s="17" t="inlineStr">
+      <c r="D89" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10754,7 +10994,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D90" s="17" t="inlineStr">
+      <c r="D90" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10786,7 +11026,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D91" s="17" t="inlineStr">
+      <c r="D91" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10818,7 +11058,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D92" s="17" t="inlineStr">
+      <c r="D92" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10850,7 +11090,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D93" s="17" t="inlineStr">
+      <c r="D93" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10882,7 +11122,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D94" s="17" t="inlineStr">
+      <c r="D94" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10914,7 +11154,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D95" s="17" t="inlineStr">
+      <c r="D95" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -10978,7 +11218,7 @@
           <t>TIME</t>
         </is>
       </c>
-      <c r="D97" s="17" t="inlineStr">
+      <c r="D97" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11010,7 +11250,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D98" s="17" t="inlineStr">
+      <c r="D98" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11042,7 +11282,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D99" s="17" t="inlineStr">
+      <c r="D99" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11074,7 +11314,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D100" s="17" t="inlineStr">
+      <c r="D100" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11106,7 +11346,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D101" s="17" t="inlineStr">
+      <c r="D101" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11138,7 +11378,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D102" s="17" t="inlineStr">
+      <c r="D102" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11170,7 +11410,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D103" s="17" t="inlineStr">
+      <c r="D103" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11202,7 +11442,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D104" s="18" t="inlineStr">
+      <c r="D104" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -11234,7 +11474,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D105" s="17" t="inlineStr">
+      <c r="D105" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11266,7 +11506,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D106" s="17" t="inlineStr">
+      <c r="D106" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11298,7 +11538,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D107" s="17" t="inlineStr">
+      <c r="D107" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11330,7 +11570,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D108" s="17" t="inlineStr">
+      <c r="D108" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11362,7 +11602,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D109" s="17" t="inlineStr">
+      <c r="D109" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11394,7 +11634,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D110" s="17" t="inlineStr">
+      <c r="D110" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11426,7 +11666,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D111" s="17" t="inlineStr">
+      <c r="D111" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11458,7 +11698,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D112" s="17" t="inlineStr">
+      <c r="D112" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11586,7 +11826,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D116" s="17" t="inlineStr">
+      <c r="D116" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11650,7 +11890,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D118" s="17" t="inlineStr">
+      <c r="D118" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11682,7 +11922,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D119" s="17" t="inlineStr">
+      <c r="D119" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11842,7 +12082,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D124" s="17" t="inlineStr">
+      <c r="D124" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11874,7 +12114,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D125" s="17" t="inlineStr">
+      <c r="D125" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11906,7 +12146,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D126" s="17" t="inlineStr">
+      <c r="D126" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11938,7 +12178,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D127" s="17" t="inlineStr">
+      <c r="D127" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -11970,7 +12210,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D128" s="17" t="inlineStr">
+      <c r="D128" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12002,7 +12242,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D129" s="17" t="inlineStr">
+      <c r="D129" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12034,7 +12274,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D130" s="17" t="inlineStr">
+      <c r="D130" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12066,7 +12306,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D131" s="17" t="inlineStr">
+      <c r="D131" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12098,7 +12338,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D132" s="17" t="inlineStr">
+      <c r="D132" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12130,7 +12370,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D133" s="17" t="inlineStr">
+      <c r="D133" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12194,7 +12434,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D135" s="17" t="inlineStr">
+      <c r="D135" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12226,7 +12466,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D136" s="17" t="inlineStr">
+      <c r="D136" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12290,19 +12530,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D138" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D138" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12562,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D139" s="18" t="inlineStr">
+      <c r="D139" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -12354,7 +12594,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D140" s="17" t="inlineStr">
+      <c r="D140" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12386,7 +12626,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D141" s="18" t="inlineStr">
+      <c r="D141" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -12418,7 +12658,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D142" s="17" t="inlineStr">
+      <c r="D142" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12450,7 +12690,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D143" s="17" t="inlineStr">
+      <c r="D143" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12482,7 +12722,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D144" s="17" t="inlineStr">
+      <c r="D144" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12514,7 +12754,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D145" s="17" t="inlineStr">
+      <c r="D145" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12642,7 +12882,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D149" s="17" t="inlineStr">
+      <c r="D149" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12706,19 +12946,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D151" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D151" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -12738,7 +12978,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D152" s="18" t="inlineStr">
+      <c r="D152" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -12770,7 +13010,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D153" s="17" t="inlineStr">
+      <c r="D153" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12802,7 +13042,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D154" s="17" t="inlineStr">
+      <c r="D154" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12834,7 +13074,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D155" s="17" t="inlineStr">
+      <c r="D155" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12866,7 +13106,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D156" s="17" t="inlineStr">
+      <c r="D156" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12898,7 +13138,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D157" s="18" t="inlineStr">
+      <c r="D157" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -12930,7 +13170,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D158" s="17" t="inlineStr">
+      <c r="D158" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -12962,7 +13202,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D159" s="17" t="inlineStr">
+      <c r="D159" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13026,7 +13266,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D161" s="17" t="inlineStr">
+      <c r="D161" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13058,7 +13298,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D162" s="17" t="inlineStr">
+      <c r="D162" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13090,7 +13330,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D163" s="17" t="inlineStr">
+      <c r="D163" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13122,7 +13362,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D164" s="17" t="inlineStr">
+      <c r="D164" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13154,7 +13394,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D165" s="17" t="inlineStr">
+      <c r="D165" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13186,7 +13426,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D166" s="17" t="inlineStr">
+      <c r="D166" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13218,7 +13458,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D167" s="17" t="inlineStr">
+      <c r="D167" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13250,7 +13490,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D168" s="17" t="inlineStr">
+      <c r="D168" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13282,7 +13522,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D169" s="18" t="inlineStr">
+      <c r="D169" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -13314,7 +13554,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D170" s="17" t="inlineStr">
+      <c r="D170" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13346,7 +13586,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D171" s="17" t="inlineStr">
+      <c r="D171" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13378,7 +13618,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D172" s="18" t="inlineStr">
+      <c r="D172" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -13410,7 +13650,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D173" s="17" t="inlineStr">
+      <c r="D173" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13442,7 +13682,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D174" s="17" t="inlineStr">
+      <c r="D174" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13474,7 +13714,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D175" s="17" t="inlineStr">
+      <c r="D175" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13506,7 +13746,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D176" s="17" t="inlineStr">
+      <c r="D176" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13666,7 +13906,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D181" s="17" t="inlineStr">
+      <c r="D181" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13730,7 +13970,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D183" s="17" t="inlineStr">
+      <c r="D183" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13762,7 +14002,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D184" s="17" t="inlineStr">
+      <c r="D184" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13794,7 +14034,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D185" s="17" t="inlineStr">
+      <c r="D185" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13826,7 +14066,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D186" s="17" t="inlineStr">
+      <c r="D186" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13858,7 +14098,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D187" s="17" t="inlineStr">
+      <c r="D187" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13954,7 +14194,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D190" s="17" t="inlineStr">
+      <c r="D190" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -13986,19 +14226,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D191" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D191" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E191" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F191" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -14018,7 +14258,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D192" s="17" t="inlineStr">
+      <c r="D192" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14050,7 +14290,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D193" s="18" t="inlineStr">
+      <c r="D193" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -14082,7 +14322,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D194" s="17" t="inlineStr">
+      <c r="D194" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14114,7 +14354,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D195" s="17" t="inlineStr">
+      <c r="D195" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14146,7 +14386,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D196" s="17" t="inlineStr">
+      <c r="D196" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14178,7 +14418,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D197" s="17" t="inlineStr">
+      <c r="D197" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14242,7 +14482,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D199" s="17" t="inlineStr">
+      <c r="D199" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14274,7 +14514,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D200" s="17" t="inlineStr">
+      <c r="D200" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14402,7 +14642,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D204" s="17" t="inlineStr">
+      <c r="D204" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14434,7 +14674,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D205" s="17" t="inlineStr">
+      <c r="D205" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14466,7 +14706,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D206" s="17" t="inlineStr">
+      <c r="D206" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14498,7 +14738,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D207" s="17" t="inlineStr">
+      <c r="D207" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14530,7 +14770,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D208" s="17" t="inlineStr">
+      <c r="D208" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14562,7 +14802,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D209" s="17" t="inlineStr">
+      <c r="D209" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14594,7 +14834,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D210" s="17" t="inlineStr">
+      <c r="D210" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14626,7 +14866,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D211" s="17" t="inlineStr">
+      <c r="D211" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14658,7 +14898,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D212" s="17" t="inlineStr">
+      <c r="D212" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14690,7 +14930,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D213" s="17" t="inlineStr">
+      <c r="D213" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14722,7 +14962,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D214" s="17" t="inlineStr">
+      <c r="D214" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14754,7 +14994,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D215" s="17" t="inlineStr">
+      <c r="D215" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14786,7 +15026,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D216" s="17" t="inlineStr">
+      <c r="D216" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14818,7 +15058,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D217" s="17" t="inlineStr">
+      <c r="D217" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14850,7 +15090,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D218" s="17" t="inlineStr">
+      <c r="D218" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14882,7 +15122,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D219" s="18" t="inlineStr">
+      <c r="D219" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -14914,7 +15154,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D220" s="17" t="inlineStr">
+      <c r="D220" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14946,7 +15186,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D221" s="17" t="inlineStr">
+      <c r="D221" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -14978,7 +15218,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D222" s="17" t="inlineStr">
+      <c r="D222" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -15010,7 +15250,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D223" s="17" t="inlineStr">
+      <c r="D223" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -15202,7 +15442,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D229" s="17" t="inlineStr">
+      <c r="D229" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -15234,7 +15474,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D230" s="17" t="inlineStr">
+      <c r="D230" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -15266,7 +15506,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D231" s="18" t="inlineStr">
+      <c r="D231" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -15298,7 +15538,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D232" s="17" t="inlineStr">
+      <c r="D232" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -15330,7 +15570,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D233" s="17" t="inlineStr">
+      <c r="D233" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -15362,7 +15602,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D234" s="17" t="inlineStr">
+      <c r="D234" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -15394,7 +15634,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D235" s="17" t="inlineStr">
+      <c r="D235" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -15522,7 +15762,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D239" s="17" t="inlineStr">
+      <c r="D239" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -15714,19 +15954,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D245" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D245" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E245" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F245" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -15746,7 +15986,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D246" s="17" t="inlineStr">
+      <c r="D246" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -15778,7 +16018,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D247" s="17" t="inlineStr">
+      <c r="D247" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -15810,7 +16050,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D248" s="18" t="inlineStr">
+      <c r="D248" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -15842,7 +16082,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D249" s="17" t="inlineStr">
+      <c r="D249" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -15874,7 +16114,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D250" s="17" t="inlineStr">
+      <c r="D250" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -15906,7 +16146,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D251" s="17" t="inlineStr">
+      <c r="D251" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -15938,7 +16178,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D252" s="17" t="inlineStr">
+      <c r="D252" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16002,7 +16242,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D254" s="17" t="inlineStr">
+      <c r="D254" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16098,7 +16338,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D257" s="17" t="inlineStr">
+      <c r="D257" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16162,7 +16402,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D259" s="17" t="inlineStr">
+      <c r="D259" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16194,7 +16434,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D260" s="17" t="inlineStr">
+      <c r="D260" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16258,7 +16498,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D262" s="17" t="inlineStr">
+      <c r="D262" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16290,7 +16530,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D263" s="17" t="inlineStr">
+      <c r="D263" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16322,7 +16562,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D264" s="17" t="inlineStr">
+      <c r="D264" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16354,7 +16594,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D265" s="17" t="inlineStr">
+      <c r="D265" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16386,7 +16626,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D266" s="17" t="inlineStr">
+      <c r="D266" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16418,7 +16658,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D267" s="17" t="inlineStr">
+      <c r="D267" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16450,7 +16690,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D268" s="18" t="inlineStr">
+      <c r="D268" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -16482,7 +16722,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D269" s="17" t="inlineStr">
+      <c r="D269" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16514,7 +16754,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D270" s="17" t="inlineStr">
+      <c r="D270" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16546,7 +16786,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D271" s="17" t="inlineStr">
+      <c r="D271" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16578,7 +16818,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D272" s="17" t="inlineStr">
+      <c r="D272" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16738,7 +16978,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D277" s="17" t="inlineStr">
+      <c r="D277" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16802,7 +17042,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D279" s="17" t="inlineStr">
+      <c r="D279" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16834,7 +17074,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D280" s="17" t="inlineStr">
+      <c r="D280" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16866,7 +17106,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D281" s="17" t="inlineStr">
+      <c r="D281" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16898,7 +17138,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D282" s="18" t="inlineStr">
+      <c r="D282" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -16930,7 +17170,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D283" s="17" t="inlineStr">
+      <c r="D283" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16962,7 +17202,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D284" s="17" t="inlineStr">
+      <c r="D284" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -16994,7 +17234,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D285" s="17" t="inlineStr">
+      <c r="D285" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17026,7 +17266,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D286" s="17" t="inlineStr">
+      <c r="D286" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17058,7 +17298,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D287" s="17" t="inlineStr">
+      <c r="D287" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17154,7 +17394,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D290" s="17" t="inlineStr">
+      <c r="D290" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17186,7 +17426,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D291" s="17" t="inlineStr">
+      <c r="D291" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17218,7 +17458,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D292" s="17" t="inlineStr">
+      <c r="D292" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17250,7 +17490,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D293" s="17" t="inlineStr">
+      <c r="D293" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17282,7 +17522,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D294" s="18" t="inlineStr">
+      <c r="D294" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -17314,7 +17554,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D295" s="17" t="inlineStr">
+      <c r="D295" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17346,7 +17586,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D296" s="17" t="inlineStr">
+      <c r="D296" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17378,7 +17618,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D297" s="17" t="inlineStr">
+      <c r="D297" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17410,7 +17650,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D298" s="17" t="inlineStr">
+      <c r="D298" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17634,7 +17874,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D305" s="17" t="inlineStr">
+      <c r="D305" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17666,7 +17906,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D306" s="17" t="inlineStr">
+      <c r="D306" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17698,7 +17938,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D307" s="17" t="inlineStr">
+      <c r="D307" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17730,7 +17970,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D308" s="18" t="inlineStr">
+      <c r="D308" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -17762,7 +18002,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D309" s="17" t="inlineStr">
+      <c r="D309" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17794,7 +18034,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D310" s="17" t="inlineStr">
+      <c r="D310" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17826,7 +18066,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D311" s="17" t="inlineStr">
+      <c r="D311" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -17858,7 +18098,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D312" s="17" t="inlineStr">
+      <c r="D312" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18018,7 +18258,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D317" s="17" t="inlineStr">
+      <c r="D317" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18050,7 +18290,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D318" s="18" t="inlineStr">
+      <c r="D318" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -18082,7 +18322,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D319" s="17" t="inlineStr">
+      <c r="D319" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18114,7 +18354,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D320" s="17" t="inlineStr">
+      <c r="D320" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18178,7 +18418,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D322" s="17" t="inlineStr">
+      <c r="D322" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18210,7 +18450,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D323" s="17" t="inlineStr">
+      <c r="D323" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18242,7 +18482,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D324" s="17" t="inlineStr">
+      <c r="D324" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18338,9 +18578,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D327" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D327" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E327" s="11" t="inlineStr">
@@ -18350,7 +18590,7 @@
       </c>
       <c r="F327" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -18402,7 +18642,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D329" s="17" t="inlineStr">
+      <c r="D329" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18498,7 +18738,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D332" s="17" t="inlineStr">
+      <c r="D332" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18530,7 +18770,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D333" s="17" t="inlineStr">
+      <c r="D333" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18562,7 +18802,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D334" s="17" t="inlineStr">
+      <c r="D334" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18594,7 +18834,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D335" s="17" t="inlineStr">
+      <c r="D335" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18658,7 +18898,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D337" s="17" t="inlineStr">
+      <c r="D337" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18722,7 +18962,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D339" s="17" t="inlineStr">
+      <c r="D339" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18786,7 +19026,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D341" s="17" t="inlineStr">
+      <c r="D341" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18818,7 +19058,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D342" s="17" t="inlineStr">
+      <c r="D342" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18850,7 +19090,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D343" s="17" t="inlineStr">
+      <c r="D343" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18882,7 +19122,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D344" s="17" t="inlineStr">
+      <c r="D344" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18914,7 +19154,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D345" s="17" t="inlineStr">
+      <c r="D345" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -18978,7 +19218,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D347" s="17" t="inlineStr">
+      <c r="D347" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19074,7 +19314,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D350" s="17" t="inlineStr">
+      <c r="D350" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19106,7 +19346,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D351" s="17" t="inlineStr">
+      <c r="D351" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19138,7 +19378,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D352" s="17" t="inlineStr">
+      <c r="D352" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19170,7 +19410,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D353" s="17" t="inlineStr">
+      <c r="D353" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19202,7 +19442,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D354" s="17" t="inlineStr">
+      <c r="D354" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19234,7 +19474,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D355" s="17" t="inlineStr">
+      <c r="D355" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19266,7 +19506,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D356" s="17" t="inlineStr">
+      <c r="D356" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19298,7 +19538,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D357" s="17" t="inlineStr">
+      <c r="D357" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19330,7 +19570,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D358" s="17" t="inlineStr">
+      <c r="D358" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19362,7 +19602,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D359" s="17" t="inlineStr">
+      <c r="D359" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19426,7 +19666,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D361" s="17" t="inlineStr">
+      <c r="D361" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19490,7 +19730,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D363" s="17" t="inlineStr">
+      <c r="D363" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19522,7 +19762,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D364" s="18" t="inlineStr">
+      <c r="D364" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -19554,7 +19794,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D365" s="18" t="inlineStr">
+      <c r="D365" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -19586,7 +19826,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D366" s="17" t="inlineStr">
+      <c r="D366" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19618,7 +19858,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D367" s="17" t="inlineStr">
+      <c r="D367" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19650,7 +19890,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D368" s="17" t="inlineStr">
+      <c r="D368" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19682,7 +19922,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D369" s="17" t="inlineStr">
+      <c r="D369" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19778,7 +20018,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D372" s="17" t="inlineStr">
+      <c r="D372" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19810,7 +20050,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D373" s="18" t="inlineStr">
+      <c r="D373" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -19842,7 +20082,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D374" s="17" t="inlineStr">
+      <c r="D374" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19874,7 +20114,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D375" s="17" t="inlineStr">
+      <c r="D375" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19906,7 +20146,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D376" s="18" t="inlineStr">
+      <c r="D376" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -19938,7 +20178,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D377" s="17" t="inlineStr">
+      <c r="D377" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -19970,7 +20210,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D378" s="17" t="inlineStr">
+      <c r="D378" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20002,7 +20242,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D379" s="17" t="inlineStr">
+      <c r="D379" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20034,7 +20274,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D380" s="17" t="inlineStr">
+      <c r="D380" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20290,7 +20530,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D388" s="17" t="inlineStr">
+      <c r="D388" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20322,7 +20562,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D389" s="17" t="inlineStr">
+      <c r="D389" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20354,7 +20594,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D390" s="17" t="inlineStr">
+      <c r="D390" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20482,7 +20722,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D394" s="17" t="inlineStr">
+      <c r="D394" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20514,7 +20754,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D395" s="17" t="inlineStr">
+      <c r="D395" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20546,7 +20786,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D396" s="18" t="inlineStr">
+      <c r="D396" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -20578,7 +20818,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D397" s="17" t="inlineStr">
+      <c r="D397" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20642,7 +20882,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D399" s="17" t="inlineStr">
+      <c r="D399" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20674,7 +20914,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D400" s="17" t="inlineStr">
+      <c r="D400" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20706,7 +20946,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D401" s="17" t="inlineStr">
+      <c r="D401" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20738,7 +20978,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D402" s="17" t="inlineStr">
+      <c r="D402" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20770,7 +21010,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D403" s="17" t="inlineStr">
+      <c r="D403" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20802,7 +21042,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D404" s="18" t="inlineStr">
+      <c r="D404" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -20834,7 +21074,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D405" s="17" t="inlineStr">
+      <c r="D405" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20866,7 +21106,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D406" s="17" t="inlineStr">
+      <c r="D406" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -20898,19 +21138,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D407" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D407" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E407" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F407" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -21058,9 +21298,9 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D412" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D412" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E412" s="11" t="inlineStr">
@@ -21070,7 +21310,7 @@
       </c>
       <c r="F412" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명 적재 → GOLD `MKTG_CAMPAIGN_SK` (DIM_CAMPAIGN.sql)</t>
         </is>
       </c>
     </row>
@@ -21090,7 +21330,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D413" s="17" t="inlineStr">
+      <c r="D413" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -21122,7 +21362,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D414" s="17" t="inlineStr">
+      <c r="D414" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -21282,7 +21522,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D419" s="18" t="inlineStr">
+      <c r="D419" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -21378,7 +21618,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D422" s="17" t="inlineStr">
+      <c r="D422" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -21410,7 +21650,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D423" s="18" t="inlineStr">
+      <c r="D423" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -21442,7 +21682,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D424" s="17" t="inlineStr">
+      <c r="D424" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -21474,7 +21714,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D425" s="17" t="inlineStr">
+      <c r="D425" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -21538,7 +21778,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D427" s="17" t="inlineStr">
+      <c r="D427" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -21570,7 +21810,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D428" s="17" t="inlineStr">
+      <c r="D428" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -21762,7 +22002,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D434" s="17" t="inlineStr">
+      <c r="D434" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -21794,7 +22034,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D435" s="18" t="inlineStr">
+      <c r="D435" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -21826,7 +22066,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D436" s="17" t="inlineStr">
+      <c r="D436" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -21858,7 +22098,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D437" s="17" t="inlineStr">
+      <c r="D437" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -21890,7 +22130,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D438" s="17" t="inlineStr">
+      <c r="D438" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -21922,7 +22162,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D439" s="17" t="inlineStr">
+      <c r="D439" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -21954,19 +22194,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D440" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D440" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E440" s="11" t="inlineStr">
         <is>
-          <t>중간(SQL참조)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F440" s="11" t="inlineStr">
         <is>
-          <t>SILVER SQL 토큰 참조</t>
+          <t>개명 적재 → GOLD `MKTG_CAMPAIGN_BK` (DIM_MARKETING_CAMPAIGN.sql)</t>
         </is>
       </c>
     </row>
@@ -21986,9 +22226,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D441" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D441" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E441" s="11" t="inlineStr">
@@ -21998,7 +22238,7 @@
       </c>
       <c r="F441" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명 적재 → GOLD `MKTG_CAMPAIGN_NAME` (DIM_MARKETING_CAMPAIGN.sql)</t>
         </is>
       </c>
     </row>
@@ -22018,7 +22258,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D442" s="18" t="inlineStr">
+      <c r="D442" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -22050,19 +22290,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D443" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D443" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E443" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F443" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -22082,7 +22322,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D444" s="17" t="inlineStr">
+      <c r="D444" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -22114,7 +22354,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D445" s="18" t="inlineStr">
+      <c r="D445" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -22146,7 +22386,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D446" s="17" t="inlineStr">
+      <c r="D446" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -22178,7 +22418,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D447" s="17" t="inlineStr">
+      <c r="D447" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -22210,7 +22450,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D448" s="17" t="inlineStr">
+      <c r="D448" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -22242,7 +22482,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D449" s="17" t="inlineStr">
+      <c r="D449" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -22274,9 +22514,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D450" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D450" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E450" s="11" t="inlineStr">
@@ -22286,7 +22526,7 @@
       </c>
       <c r="F450" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명 적재 → GOLD `SPONSORSHIP_BK` (DIM_SPONSORSHIP.sql)</t>
         </is>
       </c>
     </row>
@@ -22498,19 +22738,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D457" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D457" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E457" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F457" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -22530,7 +22770,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D458" s="18" t="inlineStr">
+      <c r="D458" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -22562,7 +22802,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D459" s="17" t="inlineStr">
+      <c r="D459" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -22594,7 +22834,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D460" s="18" t="inlineStr">
+      <c r="D460" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -22626,7 +22866,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D461" s="17" t="inlineStr">
+      <c r="D461" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -22658,7 +22898,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D462" s="17" t="inlineStr">
+      <c r="D462" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -22690,7 +22930,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D463" s="17" t="inlineStr">
+      <c r="D463" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -22722,7 +22962,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D464" s="17" t="inlineStr">
+      <c r="D464" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -22946,19 +23186,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D471" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D471" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E471" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(브랜치별 상이)</t>
         </is>
       </c>
       <c r="F471" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명 적재 → GOLD `ORG_SK` (FACT_MEMBER_EVENT.sql) · ⚠️ 일부 브랜치는 센티넬 — FACT_MEMBER_EVENT.sql:237 `0 as ORG_SK`</t>
         </is>
       </c>
     </row>
@@ -23010,9 +23250,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D473" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D473" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E473" s="11" t="inlineStr">
@@ -23022,7 +23262,7 @@
       </c>
       <c r="F473" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -23170,7 +23410,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D478" s="17" t="inlineStr">
+      <c r="D478" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -23234,19 +23474,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D480" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D480" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E480" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(브랜치별 상이)</t>
         </is>
       </c>
       <c r="F480" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명 적재 → GOLD `SPONSORSHIP_SK` (FACT_MEMBER_EVENT.sql) · ⚠️ 일부 브랜치는 센티넬 — FACT_MEMBER_EVENT.sql:232 `0 as SPONSORSHIP_SK`</t>
         </is>
       </c>
     </row>
@@ -23362,7 +23602,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D484" s="17" t="inlineStr">
+      <c r="D484" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -23394,7 +23634,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D485" s="17" t="inlineStr">
+      <c r="D485" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -23426,7 +23666,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D486" s="17" t="inlineStr">
+      <c r="D486" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -23458,7 +23698,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D487" s="17" t="inlineStr">
+      <c r="D487" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -23874,7 +24114,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D500" s="17" t="inlineStr">
+      <c r="D500" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -23906,7 +24146,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D501" s="17" t="inlineStr">
+      <c r="D501" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -23938,7 +24178,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D502" s="17" t="inlineStr">
+      <c r="D502" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -23970,7 +24210,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D503" s="17" t="inlineStr">
+      <c r="D503" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -24002,7 +24242,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D504" s="17" t="inlineStr">
+      <c r="D504" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -24226,7 +24466,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D511" s="17" t="inlineStr">
+      <c r="D511" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -24258,7 +24498,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D512" s="17" t="inlineStr">
+      <c r="D512" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -24290,7 +24530,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D513" s="18" t="inlineStr">
+      <c r="D513" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -24354,7 +24594,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D515" s="17" t="inlineStr">
+      <c r="D515" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -24418,7 +24658,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D517" s="17" t="inlineStr">
+      <c r="D517" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -24450,7 +24690,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D518" s="17" t="inlineStr">
+      <c r="D518" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -24674,9 +24914,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D525" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D525" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E525" s="11" t="inlineStr">
@@ -24686,7 +24926,7 @@
       </c>
       <c r="F525" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -24834,7 +25074,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D530" s="17" t="inlineStr">
+      <c r="D530" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -24930,7 +25170,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D533" s="17" t="inlineStr">
+      <c r="D533" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -24962,7 +25202,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D534" s="17" t="inlineStr">
+      <c r="D534" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -24994,7 +25234,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D535" s="17" t="inlineStr">
+      <c r="D535" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -25154,7 +25394,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D540" s="17" t="inlineStr">
+      <c r="D540" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -25186,7 +25426,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D541" s="17" t="inlineStr">
+      <c r="D541" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -25218,7 +25458,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D542" s="17" t="inlineStr">
+      <c r="D542" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -25474,7 +25714,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D550" s="17" t="inlineStr">
+      <c r="D550" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -25506,7 +25746,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D551" s="17" t="inlineStr">
+      <c r="D551" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -25730,7 +25970,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D558" s="17" t="inlineStr">
+      <c r="D558" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -25762,7 +26002,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D559" s="17" t="inlineStr">
+      <c r="D559" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -25794,7 +26034,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D560" s="17" t="inlineStr">
+      <c r="D560" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26178,7 +26418,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D572" s="17" t="inlineStr">
+      <c r="D572" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26210,7 +26450,7 @@
           <t>BOOLEAN</t>
         </is>
       </c>
-      <c r="D573" s="17" t="inlineStr">
+      <c r="D573" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26242,7 +26482,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D574" s="17" t="inlineStr">
+      <c r="D574" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26274,7 +26514,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D575" s="17" t="inlineStr">
+      <c r="D575" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26306,7 +26546,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D576" s="17" t="inlineStr">
+      <c r="D576" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26338,7 +26578,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D577" s="17" t="inlineStr">
+      <c r="D577" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26370,7 +26610,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D578" s="18" t="inlineStr">
+      <c r="D578" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -26434,7 +26674,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D580" s="17" t="inlineStr">
+      <c r="D580" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26466,7 +26706,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D581" s="17" t="inlineStr">
+      <c r="D581" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26498,7 +26738,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D582" s="17" t="inlineStr">
+      <c r="D582" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26626,7 +26866,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D586" s="17" t="inlineStr">
+      <c r="D586" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26690,7 +26930,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D588" s="17" t="inlineStr">
+      <c r="D588" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26722,7 +26962,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D589" s="17" t="inlineStr">
+      <c r="D589" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26818,7 +27058,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D592" s="17" t="inlineStr">
+      <c r="D592" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26850,7 +27090,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D593" s="17" t="inlineStr">
+      <c r="D593" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26882,7 +27122,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D594" s="17" t="inlineStr">
+      <c r="D594" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -26946,7 +27186,7 @@
           <t>BOOLEAN</t>
         </is>
       </c>
-      <c r="D596" s="17" t="inlineStr">
+      <c r="D596" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27010,7 +27250,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D598" s="17" t="inlineStr">
+      <c r="D598" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27042,19 +27282,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D599" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D599" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E599" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F599" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -27074,7 +27314,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D600" s="17" t="inlineStr">
+      <c r="D600" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27106,7 +27346,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D601" s="18" t="inlineStr">
+      <c r="D601" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -27138,7 +27378,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D602" s="17" t="inlineStr">
+      <c r="D602" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27170,7 +27410,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D603" s="17" t="inlineStr">
+      <c r="D603" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27202,7 +27442,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D604" s="17" t="inlineStr">
+      <c r="D604" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27234,7 +27474,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D605" s="17" t="inlineStr">
+      <c r="D605" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27266,7 +27506,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D606" s="17" t="inlineStr">
+      <c r="D606" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27298,7 +27538,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D607" s="17" t="inlineStr">
+      <c r="D607" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27330,7 +27570,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D608" s="18" t="inlineStr">
+      <c r="D608" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -27362,7 +27602,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D609" s="17" t="inlineStr">
+      <c r="D609" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27394,7 +27634,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D610" s="17" t="inlineStr">
+      <c r="D610" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27426,7 +27666,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D611" s="17" t="inlineStr">
+      <c r="D611" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27458,7 +27698,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D612" s="17" t="inlineStr">
+      <c r="D612" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27490,7 +27730,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D613" s="17" t="inlineStr">
+      <c r="D613" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27522,7 +27762,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D614" s="17" t="inlineStr">
+      <c r="D614" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27554,7 +27794,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D615" s="17" t="inlineStr">
+      <c r="D615" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27586,7 +27826,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D616" s="17" t="inlineStr">
+      <c r="D616" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27618,7 +27858,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D617" s="17" t="inlineStr">
+      <c r="D617" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27682,7 +27922,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D619" s="17" t="inlineStr">
+      <c r="D619" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27714,7 +27954,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D620" s="17" t="inlineStr">
+      <c r="D620" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27842,7 +28082,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D624" s="17" t="inlineStr">
+      <c r="D624" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27874,7 +28114,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D625" s="17" t="inlineStr">
+      <c r="D625" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27906,7 +28146,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D626" s="17" t="inlineStr">
+      <c r="D626" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27938,7 +28178,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D627" s="17" t="inlineStr">
+      <c r="D627" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -27970,7 +28210,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D628" s="17" t="inlineStr">
+      <c r="D628" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28002,7 +28242,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D629" s="18" t="inlineStr">
+      <c r="D629" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -28034,7 +28274,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D630" s="17" t="inlineStr">
+      <c r="D630" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28066,7 +28306,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D631" s="17" t="inlineStr">
+      <c r="D631" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28098,7 +28338,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D632" s="17" t="inlineStr">
+      <c r="D632" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28130,7 +28370,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D633" s="17" t="inlineStr">
+      <c r="D633" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28162,7 +28402,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D634" s="17" t="inlineStr">
+      <c r="D634" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28226,7 +28466,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D636" s="17" t="inlineStr">
+      <c r="D636" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28258,7 +28498,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D637" s="17" t="inlineStr">
+      <c r="D637" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28290,7 +28530,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D638" s="17" t="inlineStr">
+      <c r="D638" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28354,7 +28594,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D640" s="17" t="inlineStr">
+      <c r="D640" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28386,7 +28626,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D641" s="17" t="inlineStr">
+      <c r="D641" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28418,7 +28658,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D642" s="17" t="inlineStr">
+      <c r="D642" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28450,7 +28690,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D643" s="17" t="inlineStr">
+      <c r="D643" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28482,7 +28722,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D644" s="17" t="inlineStr">
+      <c r="D644" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28514,7 +28754,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D645" s="18" t="inlineStr">
+      <c r="D645" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -28546,7 +28786,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D646" s="17" t="inlineStr">
+      <c r="D646" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28578,7 +28818,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D647" s="17" t="inlineStr">
+      <c r="D647" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28610,7 +28850,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D648" s="17" t="inlineStr">
+      <c r="D648" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28642,7 +28882,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D649" s="17" t="inlineStr">
+      <c r="D649" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28834,7 +29074,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D655" s="17" t="inlineStr">
+      <c r="D655" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28866,7 +29106,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D656" s="17" t="inlineStr">
+      <c r="D656" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28898,7 +29138,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D657" s="17" t="inlineStr">
+      <c r="D657" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28930,7 +29170,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D658" s="18" t="inlineStr">
+      <c r="D658" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -28962,7 +29202,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D659" s="17" t="inlineStr">
+      <c r="D659" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -28994,7 +29234,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D660" s="17" t="inlineStr">
+      <c r="D660" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29026,7 +29266,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D661" s="17" t="inlineStr">
+      <c r="D661" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29058,7 +29298,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D662" s="17" t="inlineStr">
+      <c r="D662" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29122,7 +29362,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D664" s="17" t="inlineStr">
+      <c r="D664" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29154,7 +29394,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D665" s="17" t="inlineStr">
+      <c r="D665" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29346,7 +29586,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D671" s="17" t="inlineStr">
+      <c r="D671" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29378,7 +29618,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D672" s="17" t="inlineStr">
+      <c r="D672" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29410,7 +29650,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D673" s="17" t="inlineStr">
+      <c r="D673" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29442,7 +29682,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D674" s="17" t="inlineStr">
+      <c r="D674" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29474,7 +29714,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D675" s="17" t="inlineStr">
+      <c r="D675" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29506,7 +29746,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D676" s="17" t="inlineStr">
+      <c r="D676" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29538,7 +29778,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D677" s="17" t="inlineStr">
+      <c r="D677" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29570,7 +29810,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D678" s="17" t="inlineStr">
+      <c r="D678" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29602,7 +29842,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D679" s="18" t="inlineStr">
+      <c r="D679" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -29634,7 +29874,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D680" s="17" t="inlineStr">
+      <c r="D680" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29666,7 +29906,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D681" s="17" t="inlineStr">
+      <c r="D681" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29698,7 +29938,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D682" s="17" t="inlineStr">
+      <c r="D682" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29730,7 +29970,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D683" s="17" t="inlineStr">
+      <c r="D683" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29794,7 +30034,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D685" s="17" t="inlineStr">
+      <c r="D685" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29826,7 +30066,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D686" s="17" t="inlineStr">
+      <c r="D686" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29922,7 +30162,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D689" s="17" t="inlineStr">
+      <c r="D689" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -29954,7 +30194,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D690" s="17" t="inlineStr">
+      <c r="D690" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30018,7 +30258,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D692" s="17" t="inlineStr">
+      <c r="D692" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30050,7 +30290,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D693" s="17" t="inlineStr">
+      <c r="D693" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30082,7 +30322,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D694" s="17" t="inlineStr">
+      <c r="D694" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30114,7 +30354,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D695" s="18" t="inlineStr">
+      <c r="D695" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -30146,7 +30386,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D696" s="17" t="inlineStr">
+      <c r="D696" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30178,7 +30418,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D697" s="17" t="inlineStr">
+      <c r="D697" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30210,7 +30450,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D698" s="17" t="inlineStr">
+      <c r="D698" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30242,7 +30482,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D699" s="17" t="inlineStr">
+      <c r="D699" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30370,9 +30610,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D703" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D703" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E703" s="11" t="inlineStr">
@@ -30382,7 +30622,7 @@
       </c>
       <c r="F703" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -30402,7 +30642,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D704" s="17" t="inlineStr">
+      <c r="D704" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30434,7 +30674,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D705" s="17" t="inlineStr">
+      <c r="D705" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30466,7 +30706,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D706" s="17" t="inlineStr">
+      <c r="D706" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30498,7 +30738,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D707" s="17" t="inlineStr">
+      <c r="D707" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30530,7 +30770,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D708" s="17" t="inlineStr">
+      <c r="D708" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30562,7 +30802,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D709" s="17" t="inlineStr">
+      <c r="D709" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30626,7 +30866,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D711" s="17" t="inlineStr">
+      <c r="D711" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30786,7 +31026,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D716" s="18" t="inlineStr">
+      <c r="D716" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -30818,7 +31058,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D717" s="17" t="inlineStr">
+      <c r="D717" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30850,7 +31090,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D718" s="17" t="inlineStr">
+      <c r="D718" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30882,7 +31122,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D719" s="17" t="inlineStr">
+      <c r="D719" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30946,7 +31186,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D721" s="17" t="inlineStr">
+      <c r="D721" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -30978,19 +31218,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D722" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D722" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E722" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F722" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -31042,7 +31282,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D724" s="17" t="inlineStr">
+      <c r="D724" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -31074,7 +31314,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D725" s="18" t="inlineStr">
+      <c r="D725" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -31106,7 +31346,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D726" s="17" t="inlineStr">
+      <c r="D726" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -31138,9 +31378,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D727" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D727" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E727" s="11" t="inlineStr">
@@ -31150,7 +31390,7 @@
       </c>
       <c r="F727" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명 적재 → GOLD `SPONSORSHIP_SK` (FACT_MEMBER_FEE.sql)</t>
         </is>
       </c>
     </row>
@@ -31170,7 +31410,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D728" s="17" t="inlineStr">
+      <c r="D728" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -31202,7 +31442,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D729" s="17" t="inlineStr">
+      <c r="D729" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -31426,9 +31666,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D736" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D736" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E736" s="11" t="inlineStr">
@@ -31438,7 +31678,7 @@
       </c>
       <c r="F736" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명 적재 → GOLD `SPONSORSHIP_SK` (FACT_MEMBER_FEE.sql)</t>
         </is>
       </c>
     </row>
@@ -31490,7 +31730,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D738" s="17" t="inlineStr">
+      <c r="D738" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -31586,7 +31826,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D741" s="17" t="inlineStr">
+      <c r="D741" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -31618,7 +31858,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D742" s="17" t="inlineStr">
+      <c r="D742" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -31650,9 +31890,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D743" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D743" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E743" s="11" t="inlineStr">
@@ -31662,7 +31902,7 @@
       </c>
       <c r="F743" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>개명 적재 → GOLD `FEE_DIV_CD` (FACT_MEMBER_FEE.sql)</t>
         </is>
       </c>
     </row>
@@ -31714,7 +31954,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D745" s="17" t="inlineStr">
+      <c r="D745" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -31746,7 +31986,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D746" s="17" t="inlineStr">
+      <c r="D746" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -31778,7 +32018,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D747" s="17" t="inlineStr">
+      <c r="D747" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -31810,7 +32050,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D748" s="17" t="inlineStr">
+      <c r="D748" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -31874,9 +32114,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D750" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D750" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E750" s="11" t="inlineStr">
@@ -31886,7 +32126,7 @@
       </c>
       <c r="F750" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -31906,7 +32146,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D751" s="17" t="inlineStr">
+      <c r="D751" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -31938,7 +32178,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D752" s="17" t="inlineStr">
+      <c r="D752" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32194,7 +32434,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D760" s="17" t="inlineStr">
+      <c r="D760" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32226,7 +32466,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D761" s="17" t="inlineStr">
+      <c r="D761" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32258,7 +32498,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D762" s="17" t="inlineStr">
+      <c r="D762" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32290,7 +32530,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D763" s="17" t="inlineStr">
+      <c r="D763" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32322,7 +32562,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D764" s="17" t="inlineStr">
+      <c r="D764" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32354,7 +32594,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D765" s="17" t="inlineStr">
+      <c r="D765" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32418,7 +32658,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D767" s="17" t="inlineStr">
+      <c r="D767" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32514,7 +32754,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D770" s="17" t="inlineStr">
+      <c r="D770" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32546,7 +32786,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D771" s="17" t="inlineStr">
+      <c r="D771" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32578,7 +32818,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D772" s="17" t="inlineStr">
+      <c r="D772" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32610,7 +32850,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D773" s="17" t="inlineStr">
+      <c r="D773" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32642,7 +32882,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D774" s="17" t="inlineStr">
+      <c r="D774" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32674,7 +32914,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D775" s="17" t="inlineStr">
+      <c r="D775" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32738,19 +32978,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D777" s="17" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D777" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E777" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F777" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -32770,7 +33010,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D778" s="18" t="inlineStr">
+      <c r="D778" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -32802,7 +33042,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D779" s="17" t="inlineStr">
+      <c r="D779" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32834,7 +33074,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D780" s="17" t="inlineStr">
+      <c r="D780" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32866,7 +33106,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D781" s="17" t="inlineStr">
+      <c r="D781" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32930,7 +33170,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D783" s="17" t="inlineStr">
+      <c r="D783" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32962,7 +33202,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D784" s="17" t="inlineStr">
+      <c r="D784" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -32994,7 +33234,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D785" s="17" t="inlineStr">
+      <c r="D785" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33026,7 +33266,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D786" s="17" t="inlineStr">
+      <c r="D786" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33154,9 +33394,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D790" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D790" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E790" s="11" t="inlineStr">
@@ -33166,7 +33406,7 @@
       </c>
       <c r="F790" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -33218,7 +33458,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D792" s="17" t="inlineStr">
+      <c r="D792" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33250,7 +33490,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D793" s="17" t="inlineStr">
+      <c r="D793" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33346,7 +33586,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D796" s="17" t="inlineStr">
+      <c r="D796" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33378,7 +33618,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D797" s="17" t="inlineStr">
+      <c r="D797" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33410,7 +33650,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D798" s="17" t="inlineStr">
+      <c r="D798" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33442,7 +33682,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D799" s="17" t="inlineStr">
+      <c r="D799" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33506,7 +33746,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D801" s="17" t="inlineStr">
+      <c r="D801" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33538,7 +33778,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D802" s="17" t="inlineStr">
+      <c r="D802" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33602,7 +33842,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D804" s="17" t="inlineStr">
+      <c r="D804" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33666,7 +33906,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D806" s="17" t="inlineStr">
+      <c r="D806" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33698,7 +33938,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D807" s="17" t="inlineStr">
+      <c r="D807" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33730,7 +33970,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D808" s="17" t="inlineStr">
+      <c r="D808" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33762,7 +34002,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D809" s="17" t="inlineStr">
+      <c r="D809" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33794,7 +34034,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D810" s="17" t="inlineStr">
+      <c r="D810" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33922,7 +34162,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D814" s="17" t="inlineStr">
+      <c r="D814" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33954,7 +34194,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D815" s="17" t="inlineStr">
+      <c r="D815" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -33986,7 +34226,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D816" s="17" t="inlineStr">
+      <c r="D816" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34018,7 +34258,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D817" s="17" t="inlineStr">
+      <c r="D817" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34050,7 +34290,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D818" s="17" t="inlineStr">
+      <c r="D818" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34082,7 +34322,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D819" s="17" t="inlineStr">
+      <c r="D819" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34114,7 +34354,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D820" s="17" t="inlineStr">
+      <c r="D820" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34146,7 +34386,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D821" s="17" t="inlineStr">
+      <c r="D821" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34178,7 +34418,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D822" s="17" t="inlineStr">
+      <c r="D822" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34210,7 +34450,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D823" s="17" t="inlineStr">
+      <c r="D823" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34242,7 +34482,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D824" s="17" t="inlineStr">
+      <c r="D824" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34306,7 +34546,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D826" s="17" t="inlineStr">
+      <c r="D826" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34370,7 +34610,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D828" s="17" t="inlineStr">
+      <c r="D828" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34402,7 +34642,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D829" s="18" t="inlineStr">
+      <c r="D829" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -34434,7 +34674,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D830" s="17" t="inlineStr">
+      <c r="D830" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34466,7 +34706,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D831" s="17" t="inlineStr">
+      <c r="D831" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34498,7 +34738,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D832" s="18" t="inlineStr">
+      <c r="D832" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -34530,7 +34770,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D833" s="17" t="inlineStr">
+      <c r="D833" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34562,7 +34802,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D834" s="17" t="inlineStr">
+      <c r="D834" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34594,7 +34834,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D835" s="17" t="inlineStr">
+      <c r="D835" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34626,7 +34866,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D836" s="17" t="inlineStr">
+      <c r="D836" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34658,7 +34898,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D837" s="17" t="inlineStr">
+      <c r="D837" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34690,7 +34930,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D838" s="17" t="inlineStr">
+      <c r="D838" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34722,7 +34962,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D839" s="17" t="inlineStr">
+      <c r="D839" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34754,7 +34994,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D840" s="17" t="inlineStr">
+      <c r="D840" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34786,7 +35026,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D841" s="17" t="inlineStr">
+      <c r="D841" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34818,7 +35058,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D842" s="17" t="inlineStr">
+      <c r="D842" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34850,7 +35090,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D843" s="17" t="inlineStr">
+      <c r="D843" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34882,7 +35122,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D844" s="17" t="inlineStr">
+      <c r="D844" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34914,7 +35154,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D845" s="17" t="inlineStr">
+      <c r="D845" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34946,7 +35186,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D846" s="17" t="inlineStr">
+      <c r="D846" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -34978,7 +35218,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D847" s="17" t="inlineStr">
+      <c r="D847" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35010,7 +35250,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D848" s="17" t="inlineStr">
+      <c r="D848" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35042,7 +35282,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D849" s="17" t="inlineStr">
+      <c r="D849" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35074,7 +35314,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D850" s="17" t="inlineStr">
+      <c r="D850" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35106,7 +35346,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D851" s="17" t="inlineStr">
+      <c r="D851" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35138,7 +35378,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D852" s="17" t="inlineStr">
+      <c r="D852" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35170,7 +35410,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D853" s="18" t="inlineStr">
+      <c r="D853" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -35202,7 +35442,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D854" s="17" t="inlineStr">
+      <c r="D854" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35234,7 +35474,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D855" s="17" t="inlineStr">
+      <c r="D855" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35266,7 +35506,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D856" s="17" t="inlineStr">
+      <c r="D856" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35298,7 +35538,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D857" s="17" t="inlineStr">
+      <c r="D857" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35362,7 +35602,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D859" s="17" t="inlineStr">
+      <c r="D859" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35394,7 +35634,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D860" s="17" t="inlineStr">
+      <c r="D860" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35458,7 +35698,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D862" s="17" t="inlineStr">
+      <c r="D862" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35490,7 +35730,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D863" s="17" t="inlineStr">
+      <c r="D863" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35522,7 +35762,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D864" s="17" t="inlineStr">
+      <c r="D864" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35554,7 +35794,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D865" s="17" t="inlineStr">
+      <c r="D865" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35586,7 +35826,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D866" s="18" t="inlineStr">
+      <c r="D866" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -35618,7 +35858,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D867" s="17" t="inlineStr">
+      <c r="D867" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35650,7 +35890,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D868" s="17" t="inlineStr">
+      <c r="D868" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35682,7 +35922,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D869" s="17" t="inlineStr">
+      <c r="D869" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35714,7 +35954,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D870" s="17" t="inlineStr">
+      <c r="D870" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35746,7 +35986,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D871" s="17" t="inlineStr">
+      <c r="D871" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35778,7 +36018,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D872" s="17" t="inlineStr">
+      <c r="D872" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35842,7 +36082,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D874" s="17" t="inlineStr">
+      <c r="D874" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35874,7 +36114,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D875" s="17" t="inlineStr">
+      <c r="D875" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35906,7 +36146,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D876" s="17" t="inlineStr">
+      <c r="D876" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35938,7 +36178,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D877" s="17" t="inlineStr">
+      <c r="D877" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -35970,7 +36210,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D878" s="17" t="inlineStr">
+      <c r="D878" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36002,7 +36242,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D879" s="17" t="inlineStr">
+      <c r="D879" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36034,7 +36274,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D880" s="17" t="inlineStr">
+      <c r="D880" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36066,7 +36306,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D881" s="17" t="inlineStr">
+      <c r="D881" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36194,7 +36434,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D885" s="17" t="inlineStr">
+      <c r="D885" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36226,9 +36466,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D886" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D886" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E886" s="11" t="inlineStr">
@@ -36238,7 +36478,7 @@
       </c>
       <c r="F886" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -36258,7 +36498,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D887" s="17" t="inlineStr">
+      <c r="D887" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36354,7 +36594,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D890" s="17" t="inlineStr">
+      <c r="D890" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36386,7 +36626,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D891" s="17" t="inlineStr">
+      <c r="D891" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36482,7 +36722,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D894" s="17" t="inlineStr">
+      <c r="D894" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36514,7 +36754,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D895" s="17" t="inlineStr">
+      <c r="D895" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36546,7 +36786,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D896" s="17" t="inlineStr">
+      <c r="D896" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36578,7 +36818,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D897" s="17" t="inlineStr">
+      <c r="D897" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36610,7 +36850,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D898" s="17" t="inlineStr">
+      <c r="D898" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36642,7 +36882,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D899" s="17" t="inlineStr">
+      <c r="D899" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36674,7 +36914,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D900" s="17" t="inlineStr">
+      <c r="D900" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36706,7 +36946,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D901" s="17" t="inlineStr">
+      <c r="D901" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36834,7 +37074,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D905" s="17" t="inlineStr">
+      <c r="D905" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36930,7 +37170,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D908" s="17" t="inlineStr">
+      <c r="D908" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36962,7 +37202,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D909" s="17" t="inlineStr">
+      <c r="D909" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -36994,7 +37234,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D910" s="18" t="inlineStr">
+      <c r="D910" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -37026,7 +37266,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D911" s="17" t="inlineStr">
+      <c r="D911" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -37058,7 +37298,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D912" s="17" t="inlineStr">
+      <c r="D912" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -37090,7 +37330,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D913" s="17" t="inlineStr">
+      <c r="D913" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -37122,7 +37362,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D914" s="17" t="inlineStr">
+      <c r="D914" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -37154,7 +37394,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D915" s="17" t="inlineStr">
+      <c r="D915" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -37186,7 +37426,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D916" s="17" t="inlineStr">
+      <c r="D916" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -37218,7 +37458,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D917" s="17" t="inlineStr">
+      <c r="D917" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -37506,7 +37746,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D926" s="17" t="inlineStr">
+      <c r="D926" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -37538,7 +37778,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D927" s="18" t="inlineStr">
+      <c r="D927" s="17" t="inlineStr">
         <is>
           <t>제외(PII·본문·메타)</t>
         </is>
@@ -37602,7 +37842,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D929" s="17" t="inlineStr">
+      <c r="D929" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -37634,7 +37874,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D930" s="17" t="inlineStr">
+      <c r="D930" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -38048,7 +38288,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -38080,7 +38320,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -38112,7 +38352,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -38144,7 +38384,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -38176,7 +38416,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -38208,7 +38448,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -39838,7 +40078,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -39870,7 +40110,7 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -39902,7 +40142,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -39934,7 +40174,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40094,7 +40334,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40126,7 +40366,7 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40158,7 +40398,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40190,7 +40430,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40286,7 +40526,7 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40318,7 +40558,7 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40350,7 +40590,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40382,7 +40622,7 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40478,7 +40718,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40542,7 +40782,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40606,7 +40846,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40638,7 +40878,7 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40670,7 +40910,7 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40702,7 +40942,7 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40766,7 +41006,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D33" s="17" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40798,7 +41038,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -40894,7 +41134,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41054,7 +41294,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41086,7 +41326,7 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41118,7 +41358,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41150,7 +41390,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41246,7 +41486,7 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41278,7 +41518,7 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D49" s="17" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41310,7 +41550,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41342,7 +41582,7 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D51" s="17" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41438,7 +41678,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D54" s="17" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41502,7 +41742,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D56" s="17" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41566,7 +41806,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41598,7 +41838,7 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="D59" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41630,7 +41870,7 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D60" s="17" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41662,7 +41902,7 @@
           <t>VARIANT</t>
         </is>
       </c>
-      <c r="D61" s="17" t="inlineStr">
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41726,7 +41966,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D63" s="17" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41758,7 +41998,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41854,7 +42094,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>
@@ -41886,7 +42126,7 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>미노출(검토대상)</t>
         </is>

--- a/30_output_share/06_BRONZE노출감사.xlsx
+++ b/30_output_share/06_BRONZE노출감사.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BRONZE 노출감사 — 전 원천 1153컬럼 (2026-08-30)</t>
+          <t>BRONZE 노출감사 — 전 원천 1153컬럼 (2026-09-02)</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>72</v>
+        <v>339</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2054,20 +2054,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>INCREASE_FLAG</t>
+          <t>JOIN_DATE</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>339</v>
+        <v>294</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CAST(NULL AS BOOLEAN) as INCREASE_FLAG</t>
+          <t>CAST(NULL AS DATE) as JOIN_DATE</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2079,70 +2079,70 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>JOIN_DATE</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>340</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CAST(NULL AS DATE) as JOIN_DATE</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>FACT_MEMBER_EVENT.sql</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>JOIN_DATE</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>294</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>CAST(NULL AS DATE) as JOIN_DATE</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_SERVICE_EVENT.sql</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JOIN_DATE</t>
+          <t>MAIL_RECEIVE_FLAG</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>340</v>
+        <v>106</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CAST(NULL AS DATE) as JOIN_DATE</t>
+          <t>CAST(NULL AS BOOLEAN) as MAIL_RECEIVE_FLAG</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MAIL_RECEIVE_FLAG</t>
+          <t>MBER_INFLOW_PATH_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>106</v>
+        <v>316</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CAST(NULL AS BOOLEAN) as MAIL_RECEIVE_FLAG</t>
+          <t>CAST(NULL AS NUMBER(38,0)) as MBER_INFLOW_PATH_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2159,15 +2159,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MBER_INFLOW_PATH_CD_AT_EVENT</t>
+          <t>MBER_INFLOW_PATH_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(38,0)) as MBER_INFLOW_PATH_CD_AT_EVENT</t>
+          <t>CAST(NULL AS VARCHAR) as MBER_INFLOW_PATH_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2179,20 +2179,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_SERVICE_EVENT.sql</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MBER_INFLOW_PATH_NM_AT_EVENT</t>
+          <t>MEMBER_STOP_FLAG</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>317</v>
+        <v>107</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as MBER_INFLOW_PATH_NM_AT_EVENT</t>
+          <t>CAST(NULL AS BOOLEAN) as MEMBER_STOP_FLAG</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2204,20 +2204,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.sql</t>
+          <t>DIM_MEMBER_IDENTITY.sql</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MEMBER_STOP_FLAG</t>
+          <t>MEMNUM</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CAST(NULL AS BOOLEAN) as MEMBER_STOP_FLAG</t>
+          <t>CAST(NULL AS VARCHAR) as MEMNUM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2229,20 +2229,20 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_IDENTITY.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MEMNUM</t>
+          <t>MKTG_CMPGN_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>27</v>
+        <v>324</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as MEMNUM</t>
+          <t>CAST(NULL AS NUMBER(38,0)) as MKTG_CMPGN_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2259,15 +2259,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MKTG_CMPGN_CD_AT_EVENT</t>
+          <t>MKTG_CMPGN_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(38,0)) as MKTG_CMPGN_CD_AT_EVENT</t>
+          <t>CAST(NULL AS VARCHAR) as MKTG_CMPGN_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2284,15 +2284,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MKTG_CMPGN_NM_AT_EVENT</t>
+          <t>MKTG_UTM_AT_EVENT</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as MKTG_CMPGN_NM_AT_EVENT</t>
+          <t>CAST(NULL AS NUMBER(38,0)) as MKTG_UTM_AT_EVENT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2309,15 +2309,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MKTG_UTM_AT_EVENT</t>
+          <t>MKTG_UTM_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(38,0)) as MKTG_UTM_AT_EVENT</t>
+          <t>CAST(NULL AS VARCHAR) as MKTG_UTM_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2334,15 +2334,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MKTG_UTM_NM_AT_EVENT</t>
+          <t>NEW_EXISTING_FLAG</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>329</v>
+        <v>219</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as MKTG_UTM_NM_AT_EVENT</t>
+          <t>CAST(NULL AS VARCHAR) as NEW_EXISTING_FLAG</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2354,7 +2354,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>219</v>
+        <v>344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2384,15 +2384,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NEW_EXISTING_FLAG</t>
+          <t>NEW_FLAG</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as NEW_EXISTING_FLAG</t>
+          <t>CAST(NULL AS BOOLEAN) as NEW_FLAG</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2404,32 +2404,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>DIM_CAMPAIGN.sql</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NEW_FLAG</t>
+          <t>ORG_SK</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>339</v>
+        <v>50</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CAST(NULL AS BOOLEAN) as NEW_FLAG</t>
+          <t>0 as ORG_SK</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_ORG.sql, FACT_DEV_ACHIEVEMENT.sql, FACT_MEMBER_EVENT.sql, FACT_TARGET_BIZ.sql, FACT_TARGET_DEV.sql</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.sql</t>
+          <t>FACT_BUDGET.sql</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.sql</t>
+          <t>FACT_BUDGET_YEARLY.sql</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FACT_BUDGET_YEARLY.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>36</v>
+        <v>276</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>DIM_ORG.sql, FACT_DEV_ACHIEVEMENT.sql, FACT_MEMBER_EVENT.sql, FACT_TARGET_BIZ.sql, FACT_TARGET_DEV.sql</t>
+          <t>DIM_ORG.sql, FACT_DEV_ACHIEVEMENT.sql, FACT_TARGET_BIZ.sql, FACT_TARGET_DEV.sql</t>
         </is>
       </c>
     </row>
@@ -2509,45 +2509,45 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ORG_SK</t>
+          <t>PARENT_CAMPAIGN_NAME_AT_EVENT</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>276</v>
+        <v>336</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0 as ORG_SK</t>
+          <t>CAST(NULL AS VARCHAR) as PARENT_CAMPAIGN_NAME_AT_EVENT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>DIM_ORG.sql, FACT_DEV_ACHIEVEMENT.sql, FACT_TARGET_BIZ.sql, FACT_TARGET_DEV.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PARENT_CAMPAIGN_NAME_AT_EVENT</t>
+          <t>PAYMENT_SK</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as PARENT_CAMPAIGN_NAME_AT_EVENT</t>
+          <t>0 as PAYMENT_SK</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_PAYMENT.sql, FACT_MEMBER_FEE.sql</t>
         </is>
       </c>
     </row>
@@ -2559,20 +2559,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PAYMENT_SK</t>
+          <t>PERIOD_BAND1</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>303</v>
+        <v>342</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0 as PAYMENT_SK</t>
+          <t>CAST(NULL AS VARCHAR) as PERIOD_BAND1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>DIM_PAYMENT.sql, FACT_MEMBER_FEE.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PERIOD_BAND1</t>
+          <t>PERIOD_BAND2</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as PERIOD_BAND1</t>
+          <t>CAST(NULL AS VARCHAR) as PERIOD_BAND2</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2604,20 +2604,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>DIM_AD_CREATIVE.sql</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PERIOD_BAND2</t>
+          <t>PLATFORM_TYPE</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>342</v>
+        <v>39</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as PERIOD_BAND2</t>
+          <t>CAST(NULL AS VARCHAR) as PLATFORM_TYPE</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2629,45 +2629,45 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.sql</t>
+          <t>DIM_MEMBER.sql</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PLAN_BUDGET_YEAR</t>
+          <t>PREV_MBER_STAT_CD</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(18,2)) as PLAN_BUDGET_YEAR</t>
+          <t>CAST(NULL AS VARCHAR) as PREV_MBER_STAT_CD</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FACT_BUDGET_YEARLY.sql</t>
+          <t>WIDE_MEMBER_EVENT.sql, WIDE_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DIM_AD_CREATIVE.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PLATFORM_TYPE</t>
+          <t>PROMO_METHOD_NAME_AT_EVENT</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>32</v>
+        <v>337</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as PLATFORM_TYPE</t>
+          <t>CAST(NULL AS VARCHAR) as PROMO_METHOD_NAME_AT_EVENT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2679,45 +2679,45 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PREV_MBER_STAT_CD</t>
+          <t>REASON_SK</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>128</v>
+        <v>203</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as PREV_MBER_STAT_CD</t>
+          <t>0 as REASON_SK</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>WIDE_MEMBER_EVENT.sql, WIDE_MEMBER_MONTHLY.sql</t>
+          <t>DIM_REASON.sql, FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PROMO_METHOD_NAME_AT_EVENT</t>
+          <t>REDONATE_FLAG</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as PROMO_METHOD_NAME_AT_EVENT</t>
+          <t>CAST(NULL AS BOOLEAN) as REDONATE_FLAG</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2734,40 +2734,40 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>REASON_SK</t>
+          <t>REGION_AT_EVENT</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>203</v>
+        <v>308</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0 as REASON_SK</t>
+          <t>CAST(NULL AS VARCHAR) as REGION_AT_EVENT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>DIM_REASON.sql, FACT_MEMBER_MONTHLY.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_EVENT_PARTICIPATION.sql</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>REDONATE_FLAG</t>
+          <t>SELF_PART_FLAG</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>339</v>
+        <v>68</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CAST(NULL AS BOOLEAN) as REDONATE_FLAG</t>
+          <t>CAST(NULL AS BOOLEAN) as SELF_PART_FLAG</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2779,20 +2779,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_SERVICE_EVENT.sql</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>REGION_AT_EVENT</t>
+          <t>SEND_STATUS2</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>308</v>
+        <v>104</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as REGION_AT_EVENT</t>
+          <t>CAST(NULL AS VARCHAR) as SEND_STATUS2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2804,45 +2804,45 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DIM_AD_CREATIVE.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RT_TYPE</t>
+          <t>SEX_AT_EVENT</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as RT_TYPE</t>
+          <t>CAST(NULL AS VARCHAR) as SEX_AT_EVENT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FACT_AD_BROADCAST.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SELF_PART_FLAG</t>
+          <t>SPNSR_AMT</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>68</v>
+        <v>291</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CAST(NULL AS BOOLEAN) as SELF_PART_FLAG</t>
+          <t>CAST(NULL AS NUMBER(18,0)) as SPNSR_AMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2854,20 +2854,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SEND_STATUS2</t>
+          <t>SPNSR_DIV_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>104</v>
+        <v>330</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SEND_STATUS2</t>
+          <t>CAST(NULL AS VARCHAR) as SPNSR_DIV_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2884,15 +2884,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SEX_AT_EVENT</t>
+          <t>SPNSR_DIV_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SEX_AT_EVENT</t>
+          <t>CAST(NULL AS VARCHAR) as SPNSR_DIV_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2904,82 +2904,82 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_BUDGET.sql</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SPNSR_AMT</t>
+          <t>SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(18,0)) as SPNSR_AMT</t>
+          <t>CAST(NULL AS NUMBER(38,0)) as SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSOR_BIZ.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_BUDGET_YEARLY.sql</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SPNSR_DIV_CD_AT_EVENT</t>
+          <t>SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>330</v>
+        <v>53</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SPNSR_DIV_CD_AT_EVENT</t>
+          <t>CAST(NULL AS NUMBER(38,0)) as SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSOR_BIZ.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_EVENT_PARTICIPATION.sql</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SPNSR_DIV_NM_AT_EVENT</t>
+          <t>SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>331</v>
+        <v>34</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SPNSR_DIV_NM_AT_EVENT</t>
+          <t>0 as SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSOR_BIZ.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2988,66 +2988,66 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>25</v>
+        <v>271</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(38,0)) as SPONSORSHIP_SK</t>
+          <t>0 as SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSOR_BIZ.sql, FACT_TARGET_BIZ.sql</t>
+          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSOR_BIZ.sql, FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FACT_BUDGET_YEARLY.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_SK</t>
+          <t>STOP_CHANNEL</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>39</v>
+        <v>215</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(38,0)) as SPONSORSHIP_SK</t>
+          <t>CAST(NULL AS VARCHAR) as STOP_CHANNEL</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSOR_BIZ.sql, FACT_TARGET_BIZ.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_SK</t>
+          <t>STOP_CHANNEL_NM</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>34</v>
+        <v>218</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0 as SPONSORSHIP_SK</t>
+          <t>CAST(NULL AS VARCHAR) as STOP_CHANNEL_NM</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSOR_BIZ.sql, FACT_TARGET_BIZ.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3059,45 +3059,45 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_SK</t>
+          <t>STOP_DATE</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>271</v>
+        <v>213</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0 as SPONSORSHIP_SK</t>
+          <t>CAST(NULL AS DATE) as STOP_DATE</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSOR_BIZ.sql, FACT_TARGET_BIZ.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>STOP_DATE</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>340</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>CAST(NULL AS DATE) as STOP_DATE</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>FACT_MEMBER_EVENT.sql</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>STOP_CHANNEL</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>215</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>CAST(NULL AS VARCHAR) as STOP_CHANNEL</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -3109,15 +3109,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>STOP_CHANNEL_NM</t>
+          <t>STOP_REASON</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as STOP_CHANNEL_NM</t>
+          <t>CAST(NULL AS VARCHAR) as STOP_REASON</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3134,15 +3134,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>STOP_DATE</t>
+          <t>STOP_REASON_NM</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CAST(NULL AS DATE) as STOP_DATE</t>
+          <t>CAST(NULL AS VARCHAR) as STOP_REASON_NM</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3154,45 +3154,45 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_TARGET_BIZ.sql</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>STOP_DATE</t>
+          <t>SUPP_CUM_GOAL_CNT</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>340</v>
+        <v>23</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>CAST(NULL AS DATE) as STOP_DATE</t>
+          <t>CAST(NULL AS NUMBER(18,4)) as SUPP_CUM_GOAL_CNT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>DIM_AD_CREATIVE.sql</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>STOP_REASON</t>
+          <t>TARGET_GROUP</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>214</v>
+        <v>51</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as STOP_REASON</t>
+          <t>CAST(NULL AS VARCHAR) as TARGET_GROUP</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3204,98 +3204,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>DIM_ORG.sql</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>STOP_REASON_NM</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>217</v>
+        <v>41</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as STOP_REASON_NM</t>
+          <t>CAST(NULL AS VARCHAR) as TEAM</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>FACT_TARGET_BIZ.sql</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>SUPP_CUM_GOAL_CNT</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>23</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>CAST(NULL AS NUMBER(18,4)) as SUPP_CUM_GOAL_CNT</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>DIM_AD_CREATIVE.sql</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>TARGET_GROUP</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>37</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>CAST(NULL AS VARCHAR) as TARGET_GROUP</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>DIM_ORG.sql</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>41</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>CAST(NULL AS VARCHAR) as TEAM</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -39834,12 +39759,12 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>중간(SQL참조)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>SILVER SQL 토큰 참조</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -39866,12 +39791,12 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>낮음(토큰만)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>GOLD SQL 토큰 출현 — 적재 미확인</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -39898,12 +39823,12 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>중간(SQL참조)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>SILVER SQL 토큰 참조</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -40282,12 +40207,12 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>중간(SQL참조)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>SILVER SQL 토큰 참조</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -40314,12 +40239,12 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>중간(SQL참조)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>SILVER SQL 토큰 참조</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -40346,12 +40271,12 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>중간(SQL참조)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>SILVER SQL 토큰 참조</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -42170,12 +42095,12 @@
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>중간(SQL참조)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>SILVER SQL 토큰 참조</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
